--- a/research/traditional_assets/database/data/italy/italy_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_real_estate_operations_services.xlsx
@@ -1382,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1519,13 +1519,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.09222861635795809</v>
+      </c>
+      <c r="C2">
+        <v>10.20050112625478</v>
+      </c>
+      <c r="D2">
+        <v>7.505131126254782</v>
       </c>
       <c r="E2">
-        <v>-0.463</v>
+        <v>-0.34837</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.11463</v>
       </c>
       <c r="G2">
         <v>2.81</v>
@@ -1546,43 +1555,45 @@
         <v>-0.179</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.027029754</v>
       </c>
       <c r="N2">
-        <v>-0.179</v>
+        <v>-0.206029754</v>
       </c>
       <c r="O2">
-        <v>-0.04296</v>
+        <v>-0.04944714096</v>
       </c>
       <c r="P2">
-        <v>-0.13604</v>
+        <v>-0.15658261304</v>
       </c>
       <c r="Q2">
-        <v>0.31396</v>
+        <v>0.29341738696</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.08699283468121621</v>
+      </c>
+      <c r="T2">
+        <v>0.5670348745751713</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-1.589359636791367</v>
+      </c>
+      <c r="W2">
+        <v>0.6105710023554044</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-6.622331819964029</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1590,22 +1601,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09222861635795809</v>
+        <v>0.09412861635795811</v>
       </c>
       <c r="C3">
-        <v>10.20050112625478</v>
+        <v>9.790813038221271</v>
       </c>
       <c r="D3">
-        <v>7.505131126254782</v>
+        <v>7.210073038221272</v>
       </c>
       <c r="E3">
-        <v>-0.34837</v>
+        <v>-0.23374</v>
       </c>
       <c r="F3">
-        <v>0.11463</v>
+        <v>0.22926</v>
       </c>
       <c r="G3">
         <v>2.81</v>
@@ -1626,37 +1637,37 @@
         <v>-0.179</v>
       </c>
       <c r="M3">
-        <v>0.027029754</v>
+        <v>0.054059508</v>
       </c>
       <c r="N3">
-        <v>-0.206029754</v>
+        <v>-0.233059508</v>
       </c>
       <c r="O3">
-        <v>-0.04944714096</v>
+        <v>-0.05593428192</v>
       </c>
       <c r="P3">
-        <v>-0.15658261304</v>
+        <v>-0.17712522608</v>
       </c>
       <c r="Q3">
-        <v>0.29341738696</v>
+        <v>0.27287477392</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08699283468121621</v>
+        <v>0.08741316972898373</v>
       </c>
       <c r="T3">
-        <v>0.5670348745751713</v>
+        <v>0.5728209447238976</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-1.589359636791367</v>
+        <v>-0.7946798183956835</v>
       </c>
       <c r="W3">
-        <v>0.6105710023554044</v>
+        <v>0.4231855011777022</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1664,7 +1675,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-6.622331819964029</v>
+        <v>-3.311165909982015</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1672,22 +1683,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09412861635795811</v>
+        <v>0.0960286163579581</v>
       </c>
       <c r="C4">
-        <v>9.790813038221271</v>
+        <v>9.403447299792953</v>
       </c>
       <c r="D4">
-        <v>7.210073038221272</v>
+        <v>6.937337299792953</v>
       </c>
       <c r="E4">
-        <v>-0.23374</v>
+        <v>-0.11911</v>
       </c>
       <c r="F4">
-        <v>0.22926</v>
+        <v>0.34389</v>
       </c>
       <c r="G4">
         <v>2.81</v>
@@ -1708,37 +1719,37 @@
         <v>-0.179</v>
       </c>
       <c r="M4">
-        <v>0.054059508</v>
+        <v>0.081089262</v>
       </c>
       <c r="N4">
-        <v>-0.233059508</v>
+        <v>-0.260089262</v>
       </c>
       <c r="O4">
-        <v>-0.05593428192</v>
+        <v>-0.06242142287999999</v>
       </c>
       <c r="P4">
-        <v>-0.17712522608</v>
+        <v>-0.19766783912</v>
       </c>
       <c r="Q4">
-        <v>0.27287477392</v>
+        <v>0.25233216088</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08741316972898373</v>
+        <v>0.08784217147876708</v>
       </c>
       <c r="T4">
-        <v>0.5728209447238976</v>
+        <v>0.5787263152880615</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-0.7946798183956835</v>
+        <v>-0.5297865455971223</v>
       </c>
       <c r="W4">
-        <v>0.4231855011777022</v>
+        <v>0.3607236674518015</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1746,7 +1757,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-3.311165909982015</v>
+        <v>-2.20744393998801</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1754,22 +1765,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0960286163579581</v>
+        <v>0.09792861635795809</v>
       </c>
       <c r="C5">
-        <v>9.403447299792953</v>
+        <v>9.035963075174841</v>
       </c>
       <c r="D5">
-        <v>6.937337299792953</v>
+        <v>6.684483075174841</v>
       </c>
       <c r="E5">
-        <v>-0.11911</v>
+        <v>-0.00448000000000004</v>
       </c>
       <c r="F5">
-        <v>0.34389</v>
+        <v>0.45852</v>
       </c>
       <c r="G5">
         <v>2.81</v>
@@ -1790,37 +1801,37 @@
         <v>-0.179</v>
       </c>
       <c r="M5">
-        <v>0.081089262</v>
+        <v>0.108119016</v>
       </c>
       <c r="N5">
-        <v>-0.260089262</v>
+        <v>-0.287119016</v>
       </c>
       <c r="O5">
-        <v>-0.06242142287999999</v>
+        <v>-0.06890856383999999</v>
       </c>
       <c r="P5">
-        <v>-0.19766783912</v>
+        <v>-0.21821045216</v>
       </c>
       <c r="Q5">
-        <v>0.25233216088</v>
+        <v>0.23178954784</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08784217147876708</v>
+        <v>0.08828011076500422</v>
       </c>
       <c r="T5">
-        <v>0.5787263152880615</v>
+        <v>0.5847547144056454</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-0.5297865455971223</v>
+        <v>-0.3973399091978417</v>
       </c>
       <c r="W5">
-        <v>0.3607236674518015</v>
+        <v>0.3294927505888511</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1828,7 +1839,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-2.20744393998801</v>
+        <v>-1.655582954991007</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1836,22 +1847,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09792861635795809</v>
+        <v>0.0998286163579581</v>
       </c>
       <c r="C6">
-        <v>9.035963075174841</v>
+        <v>8.686262871661077</v>
       </c>
       <c r="D6">
-        <v>6.684483075174841</v>
+        <v>6.449412871661077</v>
       </c>
       <c r="E6">
-        <v>-0.00448000000000004</v>
+        <v>0.1101499999999999</v>
       </c>
       <c r="F6">
-        <v>0.45852</v>
+        <v>0.5731499999999999</v>
       </c>
       <c r="G6">
         <v>2.81</v>
@@ -1872,37 +1883,37 @@
         <v>-0.179</v>
       </c>
       <c r="M6">
-        <v>0.108119016</v>
+        <v>0.13514877</v>
       </c>
       <c r="N6">
-        <v>-0.287119016</v>
+        <v>-0.31414877</v>
       </c>
       <c r="O6">
-        <v>-0.06890856383999999</v>
+        <v>-0.07539570479999999</v>
       </c>
       <c r="P6">
-        <v>-0.21821045216</v>
+        <v>-0.2387530652</v>
       </c>
       <c r="Q6">
-        <v>0.23178954784</v>
+        <v>0.2112469348</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08828011076500422</v>
+        <v>0.08872726982568849</v>
       </c>
       <c r="T6">
-        <v>0.5847547144056454</v>
+        <v>0.5909100271888628</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-0.3973399091978417</v>
+        <v>-0.3178719273582734</v>
       </c>
       <c r="W6">
-        <v>0.3294927505888511</v>
+        <v>0.3107542004710809</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1910,7 +1921,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-1.655582954991007</v>
+        <v>-1.324466363992805</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1918,22 +1929,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0998286163579581</v>
+        <v>0.1017286163579581</v>
       </c>
       <c r="C7">
-        <v>8.686262871661077</v>
+        <v>8.352534219591305</v>
       </c>
       <c r="D7">
-        <v>6.449412871661077</v>
+        <v>6.230314219591306</v>
       </c>
       <c r="E7">
-        <v>0.1101499999999999</v>
+        <v>0.22478</v>
       </c>
       <c r="F7">
-        <v>0.5731499999999999</v>
+        <v>0.6877800000000001</v>
       </c>
       <c r="G7">
         <v>2.81</v>
@@ -1954,37 +1965,37 @@
         <v>-0.179</v>
       </c>
       <c r="M7">
-        <v>0.13514877</v>
+        <v>0.162178524</v>
       </c>
       <c r="N7">
-        <v>-0.31414877</v>
+        <v>-0.341178524</v>
       </c>
       <c r="O7">
-        <v>-0.07539570479999999</v>
+        <v>-0.08188284576</v>
       </c>
       <c r="P7">
-        <v>-0.2387530652</v>
+        <v>-0.25929567824</v>
       </c>
       <c r="Q7">
-        <v>0.2112469348</v>
+        <v>0.19070432176</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08872726982568849</v>
+        <v>0.08918394290894049</v>
       </c>
       <c r="T7">
-        <v>0.5909100271888628</v>
+        <v>0.5971963040738506</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-0.3178719273582734</v>
+        <v>-0.2648932727985611</v>
       </c>
       <c r="W7">
-        <v>0.3107542004710809</v>
+        <v>0.2982618337259007</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1992,7 +2003,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-1.324466363992805</v>
+        <v>-1.103721969994005</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2000,22 +2011,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1017286163579581</v>
+        <v>0.1036286163579581</v>
       </c>
       <c r="C8">
-        <v>8.352534219591305</v>
+        <v>8.033202849184152</v>
       </c>
       <c r="D8">
-        <v>6.230314219591306</v>
+        <v>6.025612849184151</v>
       </c>
       <c r="E8">
-        <v>0.2247799999999999</v>
+        <v>0.3394099999999998</v>
       </c>
       <c r="F8">
-        <v>0.6877799999999999</v>
+        <v>0.8024099999999998</v>
       </c>
       <c r="G8">
         <v>2.81</v>
@@ -2036,37 +2047,37 @@
         <v>-0.179</v>
       </c>
       <c r="M8">
-        <v>0.162178524</v>
+        <v>0.189208278</v>
       </c>
       <c r="N8">
-        <v>-0.341178524</v>
+        <v>-0.368208278</v>
       </c>
       <c r="O8">
-        <v>-0.08188284575999999</v>
+        <v>-0.08836998672</v>
       </c>
       <c r="P8">
-        <v>-0.25929567824</v>
+        <v>-0.27983829128</v>
       </c>
       <c r="Q8">
-        <v>0.19070432176</v>
+        <v>0.17016170872</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08918394290894049</v>
+        <v>0.08965043691871405</v>
       </c>
       <c r="T8">
-        <v>0.5971963040738506</v>
+        <v>0.6036177697090533</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-0.2648932727985612</v>
+        <v>-0.227051376684481</v>
       </c>
       <c r="W8">
-        <v>0.2982618337259007</v>
+        <v>0.2893387146222006</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2074,7 +2085,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-1.103721969994005</v>
+        <v>-0.9460474028520043</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2082,22 +2093,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1036286163579581</v>
+        <v>0.1055286163579581</v>
       </c>
       <c r="C9">
-        <v>8.033202849184152</v>
+        <v>7.726894804194172</v>
       </c>
       <c r="D9">
-        <v>6.025612849184152</v>
+        <v>5.833934804194173</v>
       </c>
       <c r="E9">
-        <v>0.33941</v>
+        <v>0.4540399999999999</v>
       </c>
       <c r="F9">
-        <v>0.8024100000000001</v>
+        <v>0.91704</v>
       </c>
       <c r="G9">
         <v>2.81</v>
@@ -2118,37 +2129,37 @@
         <v>-0.179</v>
       </c>
       <c r="M9">
-        <v>0.189208278</v>
+        <v>0.216238032</v>
       </c>
       <c r="N9">
-        <v>-0.368208278</v>
+        <v>-0.395238032</v>
       </c>
       <c r="O9">
-        <v>-0.08836998672</v>
+        <v>-0.09485712767999999</v>
       </c>
       <c r="P9">
-        <v>-0.27983829128</v>
+        <v>-0.30038090432</v>
       </c>
       <c r="Q9">
-        <v>0.17016170872</v>
+        <v>0.14961909568</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08965043691871405</v>
+        <v>0.09012707210261311</v>
       </c>
       <c r="T9">
-        <v>0.6036177697090533</v>
+        <v>0.6101788324232822</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.2270513766844809</v>
+        <v>-0.1986699545989209</v>
       </c>
       <c r="W9">
-        <v>0.2893387146222006</v>
+        <v>0.2826463752944255</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2156,7 +2167,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-0.9460474028520038</v>
+        <v>-0.8277914774955035</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2164,22 +2175,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1055286163579581</v>
+        <v>0.1074286163579581</v>
       </c>
       <c r="C10">
-        <v>7.726894804194172</v>
+        <v>7.432405563746737</v>
       </c>
       <c r="D10">
-        <v>5.833934804194173</v>
+        <v>5.654075563746737</v>
       </c>
       <c r="E10">
-        <v>0.4540399999999999</v>
+        <v>0.5686699999999998</v>
       </c>
       <c r="F10">
-        <v>0.91704</v>
+        <v>1.03167</v>
       </c>
       <c r="G10">
         <v>2.81</v>
@@ -2200,37 +2211,37 @@
         <v>-0.179</v>
       </c>
       <c r="M10">
-        <v>0.216238032</v>
+        <v>0.243267786</v>
       </c>
       <c r="N10">
-        <v>-0.395238032</v>
+        <v>-0.422267786</v>
       </c>
       <c r="O10">
-        <v>-0.09485712767999999</v>
+        <v>-0.10134426864</v>
       </c>
       <c r="P10">
-        <v>-0.30038090432</v>
+        <v>-0.32092351736</v>
       </c>
       <c r="Q10">
-        <v>0.14961909568</v>
+        <v>0.12907648264</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09012707210261311</v>
+        <v>0.09061418278505939</v>
       </c>
       <c r="T10">
-        <v>0.6101788324232822</v>
+        <v>0.6168840943180435</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.1986699545989209</v>
+        <v>-0.1765955151990408</v>
       </c>
       <c r="W10">
-        <v>0.2826463752944255</v>
+        <v>0.2774412224839338</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2238,7 +2249,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-0.8277914774955035</v>
+        <v>-0.7358146466626698</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2246,22 +2257,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1074286163579581</v>
+        <v>0.1093286163579581</v>
       </c>
       <c r="C11">
-        <v>7.432405563746737</v>
+        <v>7.14867470515747</v>
       </c>
       <c r="D11">
-        <v>5.654075563746737</v>
+        <v>5.48497470515747</v>
       </c>
       <c r="E11">
-        <v>0.5686699999999998</v>
+        <v>0.6832999999999998</v>
       </c>
       <c r="F11">
-        <v>1.03167</v>
+        <v>1.1463</v>
       </c>
       <c r="G11">
         <v>2.81</v>
@@ -2282,37 +2293,37 @@
         <v>-0.179</v>
       </c>
       <c r="M11">
-        <v>0.243267786</v>
+        <v>0.27029754</v>
       </c>
       <c r="N11">
-        <v>-0.422267786</v>
+        <v>-0.44929754</v>
       </c>
       <c r="O11">
-        <v>-0.10134426864</v>
+        <v>-0.1078314096</v>
       </c>
       <c r="P11">
-        <v>-0.32092351736</v>
+        <v>-0.3414661304</v>
       </c>
       <c r="Q11">
-        <v>0.12907648264</v>
+        <v>0.1085338696</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09061418278505939</v>
+        <v>0.09111211814933784</v>
       </c>
       <c r="T11">
-        <v>0.6168840943180435</v>
+        <v>0.6237383620326885</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.1765955151990408</v>
+        <v>-0.1589359636791367</v>
       </c>
       <c r="W11">
-        <v>0.2774412224839338</v>
+        <v>0.2732771002355405</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2320,7 +2331,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-0.7358146466626698</v>
+        <v>-0.6622331819964029</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2328,22 +2339,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1093286163579581</v>
+        <v>0.1112286163579581</v>
       </c>
       <c r="C12">
-        <v>7.148674705157468</v>
+        <v>6.874764981392813</v>
       </c>
       <c r="D12">
-        <v>5.484974705157469</v>
+        <v>5.325694981392813</v>
       </c>
       <c r="E12">
-        <v>0.6832999999999998</v>
+        <v>0.7979299999999998</v>
       </c>
       <c r="F12">
-        <v>1.1463</v>
+        <v>1.26093</v>
       </c>
       <c r="G12">
         <v>2.81</v>
@@ -2364,37 +2375,37 @@
         <v>-0.179</v>
       </c>
       <c r="M12">
-        <v>0.27029754</v>
+        <v>0.297327294</v>
       </c>
       <c r="N12">
-        <v>-0.44929754</v>
+        <v>-0.476327294</v>
       </c>
       <c r="O12">
-        <v>-0.1078314096</v>
+        <v>-0.11431855056</v>
       </c>
       <c r="P12">
-        <v>-0.3414661304</v>
+        <v>-0.36200874344</v>
       </c>
       <c r="Q12">
-        <v>0.1085338696</v>
+        <v>0.08799125656000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09111211814933784</v>
+        <v>0.09162124307236411</v>
       </c>
       <c r="T12">
-        <v>0.6237383620326885</v>
+        <v>0.6307466582353028</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.1589359636791367</v>
+        <v>-0.1444872397083061</v>
       </c>
       <c r="W12">
-        <v>0.2732771002355405</v>
+        <v>0.2698700911232186</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2402,7 +2413,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-0.6622331819964029</v>
+        <v>-0.6020301654512754</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2410,22 +2421,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1112286163579581</v>
+        <v>0.1131286163579581</v>
       </c>
       <c r="C13">
-        <v>6.874764981392813</v>
+        <v>6.609844941109664</v>
       </c>
       <c r="D13">
-        <v>5.325694981392813</v>
+        <v>5.175404941109663</v>
       </c>
       <c r="E13">
-        <v>0.7979299999999998</v>
+        <v>0.9125599999999998</v>
       </c>
       <c r="F13">
-        <v>1.26093</v>
+        <v>1.37556</v>
       </c>
       <c r="G13">
         <v>2.81</v>
@@ -2446,37 +2457,37 @@
         <v>-0.179</v>
       </c>
       <c r="M13">
-        <v>0.297327294</v>
+        <v>0.324357048</v>
       </c>
       <c r="N13">
-        <v>-0.476327294</v>
+        <v>-0.503357048</v>
       </c>
       <c r="O13">
-        <v>-0.11431855056</v>
+        <v>-0.12080569152</v>
       </c>
       <c r="P13">
-        <v>-0.36200874344</v>
+        <v>-0.38255135648</v>
       </c>
       <c r="Q13">
-        <v>0.08799125656000001</v>
+        <v>0.06744864351999996</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09162124307236411</v>
+        <v>0.09214193901636825</v>
       </c>
       <c r="T13">
-        <v>0.6307466582353028</v>
+        <v>0.6379142338970677</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.1444872397083061</v>
+        <v>-0.1324466363992806</v>
       </c>
       <c r="W13">
-        <v>0.2698700911232186</v>
+        <v>0.2670309168629504</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2484,7 +2495,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-0.6020301654512754</v>
+        <v>-0.5518609849970026</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2492,22 +2503,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1131286163579581</v>
+        <v>0.1150286163579581</v>
       </c>
       <c r="C14">
-        <v>6.609844941109664</v>
+        <v>6.353174410684154</v>
       </c>
       <c r="D14">
-        <v>5.175404941109663</v>
+        <v>5.033364410684154</v>
       </c>
       <c r="E14">
-        <v>0.9125599999999998</v>
+        <v>1.02719</v>
       </c>
       <c r="F14">
-        <v>1.37556</v>
+        <v>1.49019</v>
       </c>
       <c r="G14">
         <v>2.81</v>
@@ -2528,37 +2539,37 @@
         <v>-0.179</v>
       </c>
       <c r="M14">
-        <v>0.324357048</v>
+        <v>0.351386802</v>
       </c>
       <c r="N14">
-        <v>-0.503357048</v>
+        <v>-0.530386802</v>
       </c>
       <c r="O14">
-        <v>-0.12080569152</v>
+        <v>-0.12729283248</v>
       </c>
       <c r="P14">
-        <v>-0.38255135648</v>
+        <v>-0.40309396952</v>
       </c>
       <c r="Q14">
-        <v>0.06744864351999996</v>
+        <v>0.04690603048000003</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09214193901636825</v>
+        <v>0.09267460498207364</v>
       </c>
       <c r="T14">
-        <v>0.6379142338970677</v>
+        <v>0.6452465814131261</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.1324466363992806</v>
+        <v>-0.1222584335993359</v>
       </c>
       <c r="W14">
-        <v>0.2670309168629504</v>
+        <v>0.2646285386427235</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2566,7 +2577,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-0.5518609849970026</v>
+        <v>-0.5094101399972331</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2574,22 +2585,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1150286163579581</v>
+        <v>0.1169286163579581</v>
       </c>
       <c r="C15">
-        <v>6.353174410684154</v>
+        <v>6.104092303079929</v>
       </c>
       <c r="D15">
-        <v>5.033364410684154</v>
+        <v>4.898912303079928</v>
       </c>
       <c r="E15">
-        <v>1.02719</v>
+        <v>1.14182</v>
       </c>
       <c r="F15">
-        <v>1.49019</v>
+        <v>1.60482</v>
       </c>
       <c r="G15">
         <v>2.81</v>
@@ -2610,37 +2621,37 @@
         <v>-0.179</v>
       </c>
       <c r="M15">
-        <v>0.351386802</v>
+        <v>0.3784165560000001</v>
       </c>
       <c r="N15">
-        <v>-0.530386802</v>
+        <v>-0.5574165560000001</v>
       </c>
       <c r="O15">
-        <v>-0.12729283248</v>
+        <v>-0.13377997344</v>
       </c>
       <c r="P15">
-        <v>-0.40309396952</v>
+        <v>-0.42363658256</v>
       </c>
       <c r="Q15">
-        <v>0.04690603048000003</v>
+        <v>0.02636341743999998</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09267460498207364</v>
+        <v>0.09321965852837681</v>
       </c>
       <c r="T15">
-        <v>0.6452465814131261</v>
+        <v>0.65274944863886</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.1222584335993359</v>
+        <v>-0.1135256883422405</v>
       </c>
       <c r="W15">
-        <v>0.2646285386427235</v>
+        <v>0.2625693573111003</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2648,7 +2659,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-0.5094101399972331</v>
+        <v>-0.4730237014260019</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2656,22 +2667,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1169286163579581</v>
+        <v>0.1188286163579581</v>
       </c>
       <c r="C16">
-        <v>6.104092303079929</v>
+        <v>5.862006329790937</v>
       </c>
       <c r="D16">
-        <v>4.898912303079928</v>
+        <v>4.771456329790937</v>
       </c>
       <c r="E16">
-        <v>1.14182</v>
+        <v>1.25645</v>
       </c>
       <c r="F16">
-        <v>1.60482</v>
+        <v>1.71945</v>
       </c>
       <c r="G16">
         <v>2.81</v>
@@ -2692,37 +2703,37 @@
         <v>-0.179</v>
       </c>
       <c r="M16">
-        <v>0.3784165560000001</v>
+        <v>0.40544631</v>
       </c>
       <c r="N16">
-        <v>-0.5574165560000001</v>
+        <v>-0.58444631</v>
       </c>
       <c r="O16">
-        <v>-0.13377997344</v>
+        <v>-0.1402671144</v>
       </c>
       <c r="P16">
-        <v>-0.42363658256</v>
+        <v>-0.4441791956</v>
       </c>
       <c r="Q16">
-        <v>0.02636341743999998</v>
+        <v>0.00582080439999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09321965852837681</v>
+        <v>0.09377753686400478</v>
       </c>
       <c r="T16">
-        <v>0.65274944863886</v>
+        <v>0.6604288539169643</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.1135256883422405</v>
+        <v>-0.1059573091194244</v>
       </c>
       <c r="W16">
-        <v>0.2625693573111003</v>
+        <v>0.2607847334903603</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2730,7 +2741,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-0.4730237014260019</v>
+        <v>-0.4414887879976019</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2738,22 +2749,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1188286163579581</v>
+        <v>0.1207286163579581</v>
       </c>
       <c r="C17">
-        <v>5.862006329790937</v>
+        <v>5.626384278058758</v>
       </c>
       <c r="D17">
-        <v>4.771456329790937</v>
+        <v>4.650464278058758</v>
       </c>
       <c r="E17">
-        <v>1.25645</v>
+        <v>1.37108</v>
       </c>
       <c r="F17">
-        <v>1.71945</v>
+        <v>1.83408</v>
       </c>
       <c r="G17">
         <v>2.81</v>
@@ -2774,37 +2785,37 @@
         <v>-0.179</v>
       </c>
       <c r="M17">
-        <v>0.40544631</v>
+        <v>0.432476064</v>
       </c>
       <c r="N17">
-        <v>-0.5844463099999999</v>
+        <v>-0.611476064</v>
       </c>
       <c r="O17">
-        <v>-0.1402671144</v>
+        <v>-0.14675425536</v>
       </c>
       <c r="P17">
-        <v>-0.4441791956</v>
+        <v>-0.46472180864</v>
       </c>
       <c r="Q17">
-        <v>0.005820804400000046</v>
+        <v>-0.01472180864</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09377753686400478</v>
+        <v>0.09434869801714768</v>
       </c>
       <c r="T17">
-        <v>0.6604288539169643</v>
+        <v>0.6682911021778805</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.1059573091194245</v>
+        <v>-0.09933497729946043</v>
       </c>
       <c r="W17">
-        <v>0.2607847334903603</v>
+        <v>0.2592231876472128</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2812,7 +2823,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-0.4414887879976017</v>
+        <v>-0.4138957387477518</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2820,22 +2831,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1207286163579581</v>
+        <v>0.1226286163579581</v>
       </c>
       <c r="C18">
-        <v>5.626384278058758</v>
+        <v>5.396746582395677</v>
       </c>
       <c r="D18">
-        <v>4.650464278058758</v>
+        <v>4.535456582395677</v>
       </c>
       <c r="E18">
-        <v>1.37108</v>
+        <v>1.48571</v>
       </c>
       <c r="F18">
-        <v>1.83408</v>
+        <v>1.94871</v>
       </c>
       <c r="G18">
         <v>2.81</v>
@@ -2856,37 +2867,37 @@
         <v>-0.179</v>
       </c>
       <c r="M18">
-        <v>0.432476064</v>
+        <v>0.459505818</v>
       </c>
       <c r="N18">
-        <v>-0.611476064</v>
+        <v>-0.6385058180000001</v>
       </c>
       <c r="O18">
-        <v>-0.14675425536</v>
+        <v>-0.15324139632</v>
       </c>
       <c r="P18">
-        <v>-0.46472180864</v>
+        <v>-0.4852644216800001</v>
       </c>
       <c r="Q18">
-        <v>-0.01472180864</v>
+        <v>-0.03526442168000005</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09434869801714768</v>
+        <v>0.09493362208964344</v>
       </c>
       <c r="T18">
-        <v>0.6682911021778805</v>
+        <v>0.6763428022041199</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.09933497729946043</v>
+        <v>-0.09349174334066863</v>
       </c>
       <c r="W18">
-        <v>0.2592231876472128</v>
+        <v>0.2578453530797297</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2894,7 +2905,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-0.4138957387477518</v>
+        <v>-0.3895489305861195</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2902,22 +2913,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1226286163579581</v>
+        <v>0.1245286163579581</v>
       </c>
       <c r="C19">
-        <v>5.396746582395677</v>
+        <v>5.172659971760341</v>
       </c>
       <c r="D19">
-        <v>4.535456582395677</v>
+        <v>4.425999971760341</v>
       </c>
       <c r="E19">
-        <v>1.48571</v>
+        <v>1.60034</v>
       </c>
       <c r="F19">
-        <v>1.94871</v>
+        <v>2.06334</v>
       </c>
       <c r="G19">
         <v>2.81</v>
@@ -2938,37 +2949,37 @@
         <v>-0.179</v>
       </c>
       <c r="M19">
-        <v>0.459505818</v>
+        <v>0.4865355720000001</v>
       </c>
       <c r="N19">
-        <v>-0.6385058180000001</v>
+        <v>-0.665535572</v>
       </c>
       <c r="O19">
-        <v>-0.15324139632</v>
+        <v>-0.15972853728</v>
       </c>
       <c r="P19">
-        <v>-0.4852644216800001</v>
+        <v>-0.50580703472</v>
       </c>
       <c r="Q19">
-        <v>-0.03526442168000005</v>
+        <v>-0.05580703471999998</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09493362208964344</v>
+        <v>0.09553281260293178</v>
       </c>
       <c r="T19">
-        <v>0.6763428022041199</v>
+        <v>0.6845908851578287</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.09349174334066863</v>
+        <v>-0.08829775759952037</v>
       </c>
       <c r="W19">
-        <v>0.2578453530797297</v>
+        <v>0.2566206112419669</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2976,7 +2987,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-0.3895489305861195</v>
+        <v>-0.3679073233313348</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2984,22 +2995,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1245286163579581</v>
+        <v>0.1264286163579581</v>
       </c>
       <c r="C20">
-        <v>5.172659971760339</v>
+        <v>4.953732014952916</v>
       </c>
       <c r="D20">
-        <v>4.425999971760339</v>
+        <v>4.321702014952916</v>
       </c>
       <c r="E20">
-        <v>1.60034</v>
+        <v>1.71497</v>
       </c>
       <c r="F20">
-        <v>2.06334</v>
+        <v>2.17797</v>
       </c>
       <c r="G20">
         <v>2.81</v>
@@ -3020,37 +3031,37 @@
         <v>-0.179</v>
       </c>
       <c r="M20">
-        <v>0.486535572</v>
+        <v>0.5135653259999999</v>
       </c>
       <c r="N20">
-        <v>-0.665535572</v>
+        <v>-0.692565326</v>
       </c>
       <c r="O20">
-        <v>-0.15972853728</v>
+        <v>-0.16621567824</v>
       </c>
       <c r="P20">
-        <v>-0.50580703472</v>
+        <v>-0.52634964776</v>
       </c>
       <c r="Q20">
-        <v>-0.05580703471999998</v>
+        <v>-0.07634964776000003</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09553281260293178</v>
+        <v>0.09614679794370871</v>
       </c>
       <c r="T20">
-        <v>0.6845908851578287</v>
+        <v>0.6930426244807649</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.08829775759952038</v>
+        <v>-0.08365050719954563</v>
       </c>
       <c r="W20">
-        <v>0.2566206112419669</v>
+        <v>0.2555247895976529</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3058,7 +3069,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.367907323331335</v>
+        <v>-0.348543779998107</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3066,22 +3077,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1264286163579581</v>
+        <v>0.1283286163579581</v>
       </c>
       <c r="C21">
-        <v>4.953732014952916</v>
+        <v>4.739606419476127</v>
       </c>
       <c r="D21">
-        <v>4.321702014952916</v>
+        <v>4.222206419476127</v>
       </c>
       <c r="E21">
-        <v>1.71497</v>
+        <v>1.8296</v>
       </c>
       <c r="F21">
-        <v>2.17797</v>
+        <v>2.2926</v>
       </c>
       <c r="G21">
         <v>2.81</v>
@@ -3102,37 +3113,37 @@
         <v>-0.179</v>
       </c>
       <c r="M21">
-        <v>0.5135653259999999</v>
+        <v>0.54059508</v>
       </c>
       <c r="N21">
-        <v>-0.692565326</v>
+        <v>-0.7195950799999999</v>
       </c>
       <c r="O21">
-        <v>-0.16621567824</v>
+        <v>-0.1727028192</v>
       </c>
       <c r="P21">
-        <v>-0.52634964776</v>
+        <v>-0.5468922608</v>
       </c>
       <c r="Q21">
-        <v>-0.07634964776000003</v>
+        <v>-0.09689226079999996</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09614679794370871</v>
+        <v>0.09677613291800508</v>
       </c>
       <c r="T21">
-        <v>0.6930426244807649</v>
+        <v>0.7017056572867745</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.08365050719954563</v>
+        <v>-0.07946798183956835</v>
       </c>
       <c r="W21">
-        <v>0.2555247895976529</v>
+        <v>0.2545385501177702</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3140,7 +3151,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.348543779998107</v>
+        <v>-0.3311165909982015</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3148,22 +3159,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1283286163579581</v>
+        <v>0.1302286163579581</v>
       </c>
       <c r="C22">
-        <v>4.739606419476127</v>
+        <v>4.529958965169017</v>
       </c>
       <c r="D22">
-        <v>4.222206419476127</v>
+        <v>4.127188965169018</v>
       </c>
       <c r="E22">
-        <v>1.8296</v>
+        <v>1.94423</v>
       </c>
       <c r="F22">
-        <v>2.2926</v>
+        <v>2.40723</v>
       </c>
       <c r="G22">
         <v>2.81</v>
@@ -3184,37 +3195,37 @@
         <v>-0.179</v>
       </c>
       <c r="M22">
-        <v>0.54059508</v>
+        <v>0.5676248340000001</v>
       </c>
       <c r="N22">
-        <v>-0.7195950799999999</v>
+        <v>-0.7466248340000001</v>
       </c>
       <c r="O22">
-        <v>-0.1727028192</v>
+        <v>-0.17918996016</v>
       </c>
       <c r="P22">
-        <v>-0.5468922608</v>
+        <v>-0.5674348738400001</v>
       </c>
       <c r="Q22">
-        <v>-0.09689226079999996</v>
+        <v>-0.1174348738400001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09677613291800508</v>
+        <v>0.09742140042329628</v>
       </c>
       <c r="T22">
-        <v>0.7017056572867745</v>
+        <v>0.7105880073790122</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.07946798183956835</v>
+        <v>-0.07568379222816032</v>
       </c>
       <c r="W22">
-        <v>0.2545385501177702</v>
+        <v>0.2536462382074002</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3222,7 +3233,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.3311165909982015</v>
+        <v>-0.3153491342840014</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3230,22 +3241,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1302286163579581</v>
+        <v>0.1321286163579581</v>
       </c>
       <c r="C23">
-        <v>4.529958965169019</v>
+        <v>4.32449397481882</v>
       </c>
       <c r="D23">
-        <v>4.127188965169019</v>
+        <v>4.03635397481882</v>
       </c>
       <c r="E23">
-        <v>1.94423</v>
+        <v>2.05886</v>
       </c>
       <c r="F23">
-        <v>2.40723</v>
+        <v>2.52186</v>
       </c>
       <c r="G23">
         <v>2.81</v>
@@ -3266,37 +3277,37 @@
         <v>-0.179</v>
       </c>
       <c r="M23">
-        <v>0.567624834</v>
+        <v>0.5946545879999999</v>
       </c>
       <c r="N23">
-        <v>-0.7466248339999999</v>
+        <v>-0.7736545879999999</v>
       </c>
       <c r="O23">
-        <v>-0.17918996016</v>
+        <v>-0.18567710112</v>
       </c>
       <c r="P23">
-        <v>-0.5674348738399999</v>
+        <v>-0.5879774868799998</v>
       </c>
       <c r="Q23">
-        <v>-0.1174348738399999</v>
+        <v>-0.1379774868799998</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09742140042329628</v>
+        <v>0.09808321324923597</v>
       </c>
       <c r="T23">
-        <v>0.7105880073790121</v>
+        <v>0.7196981100377174</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.07568379222816034</v>
+        <v>-0.07224361985415305</v>
       </c>
       <c r="W23">
-        <v>0.2536462382074002</v>
+        <v>0.2528350455616093</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3304,7 +3315,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.3153491342840014</v>
+        <v>-0.3010150827256377</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3312,22 +3323,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1321286163579581</v>
+        <v>0.1340286163579581</v>
       </c>
       <c r="C24">
-        <v>4.32449397481882</v>
+        <v>4.122941240804256</v>
       </c>
       <c r="D24">
-        <v>4.03635397481882</v>
+        <v>3.949431240804256</v>
       </c>
       <c r="E24">
-        <v>2.05886</v>
+        <v>2.17349</v>
       </c>
       <c r="F24">
-        <v>2.52186</v>
+        <v>2.63649</v>
       </c>
       <c r="G24">
         <v>2.81</v>
@@ -3348,37 +3359,37 @@
         <v>-0.179</v>
       </c>
       <c r="M24">
-        <v>0.5946545879999999</v>
+        <v>0.621684342</v>
       </c>
       <c r="N24">
-        <v>-0.7736545879999999</v>
+        <v>-0.800684342</v>
       </c>
       <c r="O24">
-        <v>-0.18567710112</v>
+        <v>-0.19216424208</v>
       </c>
       <c r="P24">
-        <v>-0.5879774868799998</v>
+        <v>-0.60852009992</v>
       </c>
       <c r="Q24">
-        <v>-0.1379774868799998</v>
+        <v>-0.15852009992</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09808321324923597</v>
+        <v>0.09876221601870658</v>
       </c>
       <c r="T24">
-        <v>0.7196981100377174</v>
+        <v>0.729044838739506</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.07224361985415305</v>
+        <v>-0.06910259290397247</v>
       </c>
       <c r="W24">
-        <v>0.2528350455616093</v>
+        <v>0.2520943914067568</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3386,7 +3397,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.3010150827256377</v>
+        <v>-0.2879274704332186</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3394,22 +3405,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1340286163579581</v>
+        <v>0.1359286163579581</v>
       </c>
       <c r="C25">
-        <v>4.122941240804256</v>
+        <v>3.925053340475184</v>
       </c>
       <c r="D25">
-        <v>3.949431240804256</v>
+        <v>3.866173340475184</v>
       </c>
       <c r="E25">
-        <v>2.17349</v>
+        <v>2.28812</v>
       </c>
       <c r="F25">
-        <v>2.63649</v>
+        <v>2.75112</v>
       </c>
       <c r="G25">
         <v>2.81</v>
@@ -3430,37 +3441,37 @@
         <v>-0.179</v>
       </c>
       <c r="M25">
-        <v>0.621684342</v>
+        <v>0.6487140960000001</v>
       </c>
       <c r="N25">
-        <v>-0.800684342</v>
+        <v>-0.827714096</v>
       </c>
       <c r="O25">
-        <v>-0.19216424208</v>
+        <v>-0.19865138304</v>
       </c>
       <c r="P25">
-        <v>-0.60852009992</v>
+        <v>-0.62906271296</v>
       </c>
       <c r="Q25">
-        <v>-0.15852009992</v>
+        <v>-0.17906271296</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09876221601870658</v>
+        <v>0.0994590872821106</v>
       </c>
       <c r="T25">
-        <v>0.729044838739506</v>
+        <v>0.7386375339860783</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.06910259290397247</v>
+        <v>-0.06622331819964028</v>
       </c>
       <c r="W25">
-        <v>0.2520943914067568</v>
+        <v>0.2514154584314752</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3468,7 +3479,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.2879274704332186</v>
+        <v>-0.2759304924985011</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3476,22 +3487,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1359286163579581</v>
+        <v>0.1378286163579581</v>
       </c>
       <c r="C26">
-        <v>3.925053340475185</v>
+        <v>3.730603284088261</v>
       </c>
       <c r="D26">
-        <v>3.866173340475184</v>
+        <v>3.786353284088261</v>
       </c>
       <c r="E26">
-        <v>2.28812</v>
+        <v>2.40275</v>
       </c>
       <c r="F26">
-        <v>2.75112</v>
+        <v>2.86575</v>
       </c>
       <c r="G26">
         <v>2.81</v>
@@ -3512,37 +3523,37 @@
         <v>-0.179</v>
       </c>
       <c r="M26">
-        <v>0.648714096</v>
+        <v>0.67574385</v>
       </c>
       <c r="N26">
-        <v>-0.827714096</v>
+        <v>-0.85474385</v>
       </c>
       <c r="O26">
-        <v>-0.19865138304</v>
+        <v>-0.205138524</v>
       </c>
       <c r="P26">
-        <v>-0.62906271296</v>
+        <v>-0.649605326</v>
       </c>
       <c r="Q26">
-        <v>-0.17906271296</v>
+        <v>-0.199605326</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0994590872821106</v>
+        <v>0.1001745417792054</v>
       </c>
       <c r="T26">
-        <v>0.7386375339860783</v>
+        <v>0.7484860344392261</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.06622331819964029</v>
+        <v>-0.06357438547165467</v>
       </c>
       <c r="W26">
-        <v>0.2514154584314752</v>
+        <v>0.2507908400942161</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3550,7 +3561,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.2759304924985013</v>
+        <v>-0.2648932727985611</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3558,22 +3569,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1378286163579581</v>
+        <v>0.1397286163579581</v>
       </c>
       <c r="C27">
-        <v>3.730603284088261</v>
+        <v>3.53938244820975</v>
       </c>
       <c r="D27">
-        <v>3.786353284088261</v>
+        <v>3.709762448209751</v>
       </c>
       <c r="E27">
-        <v>2.40275</v>
+        <v>2.51738</v>
       </c>
       <c r="F27">
-        <v>2.86575</v>
+        <v>2.98038</v>
       </c>
       <c r="G27">
         <v>2.81</v>
@@ -3594,37 +3605,37 @@
         <v>-0.179</v>
       </c>
       <c r="M27">
-        <v>0.67574385</v>
+        <v>0.702773604</v>
       </c>
       <c r="N27">
-        <v>-0.85474385</v>
+        <v>-0.8817736039999999</v>
       </c>
       <c r="O27">
-        <v>-0.205138524</v>
+        <v>-0.21162566496</v>
       </c>
       <c r="P27">
-        <v>-0.649605326</v>
+        <v>-0.6701479390399999</v>
       </c>
       <c r="Q27">
-        <v>-0.199605326</v>
+        <v>-0.2201479390399999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1001745417792054</v>
+        <v>0.1009093328843298</v>
       </c>
       <c r="T27">
-        <v>0.7484860344392261</v>
+        <v>0.7586007105802969</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.06357438547165467</v>
+        <v>-0.06112921679966795</v>
       </c>
       <c r="W27">
-        <v>0.2507908400942161</v>
+        <v>0.2502142693213617</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3632,7 +3643,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.2648932727985611</v>
+        <v>-0.2547050699986164</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3640,22 +3651,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1397286163579581</v>
+        <v>0.1416286163579581</v>
       </c>
       <c r="C28">
-        <v>3.53938244820975</v>
+        <v>3.351198754965666</v>
       </c>
       <c r="D28">
-        <v>3.709762448209751</v>
+        <v>3.636208754965665</v>
       </c>
       <c r="E28">
-        <v>2.51738</v>
+        <v>2.63201</v>
       </c>
       <c r="F28">
-        <v>2.98038</v>
+        <v>3.09501</v>
       </c>
       <c r="G28">
         <v>2.81</v>
@@ -3676,37 +3687,37 @@
         <v>-0.179</v>
       </c>
       <c r="M28">
-        <v>0.702773604</v>
+        <v>0.729803358</v>
       </c>
       <c r="N28">
-        <v>-0.8817736039999999</v>
+        <v>-0.9088033579999999</v>
       </c>
       <c r="O28">
-        <v>-0.21162566496</v>
+        <v>-0.21811280592</v>
       </c>
       <c r="P28">
-        <v>-0.6701479390399999</v>
+        <v>-0.69069055208</v>
       </c>
       <c r="Q28">
-        <v>-0.2201479390399999</v>
+        <v>-0.24069055208</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1009093328843298</v>
+        <v>0.1016642552526083</v>
       </c>
       <c r="T28">
-        <v>0.7586007105802969</v>
+        <v>0.7689925011361912</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.06112921679966795</v>
+        <v>-0.0588651717330136</v>
       </c>
       <c r="W28">
-        <v>0.2502142693213617</v>
+        <v>0.2496804074946446</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3714,7 +3725,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.2547050699986164</v>
+        <v>-0.2452715488875565</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3722,22 +3733,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1416286163579581</v>
+        <v>0.1435286163579581</v>
       </c>
       <c r="C29">
-        <v>3.351198754965666</v>
+        <v>3.165875063681534</v>
       </c>
       <c r="D29">
-        <v>3.636208754965665</v>
+        <v>3.565515063681534</v>
       </c>
       <c r="E29">
-        <v>2.63201</v>
+        <v>2.74664</v>
       </c>
       <c r="F29">
-        <v>3.09501</v>
+        <v>3.20964</v>
       </c>
       <c r="G29">
         <v>2.81</v>
@@ -3758,37 +3769,37 @@
         <v>-0.179</v>
       </c>
       <c r="M29">
-        <v>0.729803358</v>
+        <v>0.7568331120000001</v>
       </c>
       <c r="N29">
-        <v>-0.9088033579999999</v>
+        <v>-0.9358331120000001</v>
       </c>
       <c r="O29">
-        <v>-0.21811280592</v>
+        <v>-0.22459994688</v>
       </c>
       <c r="P29">
-        <v>-0.69069055208</v>
+        <v>-0.7112331651200001</v>
       </c>
       <c r="Q29">
-        <v>-0.24069055208</v>
+        <v>-0.2612331651200001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1016642552526083</v>
+        <v>0.1024401476866723</v>
       </c>
       <c r="T29">
-        <v>0.7689925011361912</v>
+        <v>0.7796729525408606</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.0588651717330136</v>
+        <v>-0.05676284417112024</v>
       </c>
       <c r="W29">
-        <v>0.2496804074946446</v>
+        <v>0.2491846786555502</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3796,7 +3807,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.2452715488875565</v>
+        <v>-0.2365118507130008</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3804,22 +3815,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1435286163579581</v>
+        <v>0.1454286163579581</v>
       </c>
       <c r="C30">
-        <v>3.165875063681534</v>
+        <v>2.983247746558764</v>
       </c>
       <c r="D30">
-        <v>3.565515063681534</v>
+        <v>3.497517746558763</v>
       </c>
       <c r="E30">
-        <v>2.74664</v>
+        <v>2.86127</v>
       </c>
       <c r="F30">
-        <v>3.20964</v>
+        <v>3.32427</v>
       </c>
       <c r="G30">
         <v>2.81</v>
@@ -3840,37 +3851,37 @@
         <v>-0.179</v>
       </c>
       <c r="M30">
-        <v>0.7568331120000001</v>
+        <v>0.7838628660000001</v>
       </c>
       <c r="N30">
-        <v>-0.9358331120000001</v>
+        <v>-0.962862866</v>
       </c>
       <c r="O30">
-        <v>-0.22459994688</v>
+        <v>-0.23108708784</v>
       </c>
       <c r="P30">
-        <v>-0.7112331651200001</v>
+        <v>-0.7317757781600001</v>
       </c>
       <c r="Q30">
-        <v>-0.2612331651200001</v>
+        <v>-0.28177577816</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1024401476866723</v>
+        <v>0.1032378962456395</v>
       </c>
       <c r="T30">
-        <v>0.7796729525408606</v>
+        <v>0.7906542617315769</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.05676284417112024</v>
+        <v>-0.05480550471694368</v>
       </c>
       <c r="W30">
-        <v>0.2491846786555502</v>
+        <v>0.2487231380122553</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3878,7 +3889,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.2365118507130008</v>
+        <v>-0.2283562696539319</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3886,22 +3897,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1454286163579581</v>
+        <v>0.1473286163579581</v>
       </c>
       <c r="C31">
-        <v>2.983247746558765</v>
+        <v>2.803165424279176</v>
       </c>
       <c r="D31">
-        <v>3.497517746558763</v>
+        <v>3.432065424279176</v>
       </c>
       <c r="E31">
-        <v>2.861269999999999</v>
+        <v>2.9759</v>
       </c>
       <c r="F31">
-        <v>3.324269999999999</v>
+        <v>3.4389</v>
       </c>
       <c r="G31">
         <v>2.81</v>
@@ -3922,37 +3933,37 @@
         <v>-0.179</v>
       </c>
       <c r="M31">
-        <v>0.7838628659999999</v>
+        <v>0.81089262</v>
       </c>
       <c r="N31">
-        <v>-0.9628628659999998</v>
+        <v>-0.98989262</v>
       </c>
       <c r="O31">
-        <v>-0.23108708784</v>
+        <v>-0.2375742288</v>
       </c>
       <c r="P31">
-        <v>-0.7317757781599998</v>
+        <v>-0.7523183912</v>
       </c>
       <c r="Q31">
-        <v>-0.2817757781599998</v>
+        <v>-0.3023183912</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1032378962456395</v>
+        <v>0.1040584376205772</v>
       </c>
       <c r="T31">
-        <v>0.7906542617315769</v>
+        <v>0.8019493226134566</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.0548055047169437</v>
+        <v>-0.05297865455971223</v>
       </c>
       <c r="W31">
-        <v>0.2487231380122553</v>
+        <v>0.2482923667451802</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3960,7 +3971,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.2283562696539321</v>
+        <v>-0.220744393998801</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3968,22 +3979,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1473286163579581</v>
+        <v>0.1492286163579581</v>
       </c>
       <c r="C32">
-        <v>2.803165424279176</v>
+        <v>2.625487840972425</v>
       </c>
       <c r="D32">
-        <v>3.432065424279176</v>
+        <v>3.369017840972425</v>
       </c>
       <c r="E32">
-        <v>2.9759</v>
+        <v>3.09053</v>
       </c>
       <c r="F32">
-        <v>3.4389</v>
+        <v>3.55353</v>
       </c>
       <c r="G32">
         <v>2.81</v>
@@ -4004,37 +4015,37 @@
         <v>-0.179</v>
       </c>
       <c r="M32">
-        <v>0.81089262</v>
+        <v>0.837922374</v>
       </c>
       <c r="N32">
-        <v>-0.98989262</v>
+        <v>-1.016922374</v>
       </c>
       <c r="O32">
-        <v>-0.2375742288</v>
+        <v>-0.24406136976</v>
       </c>
       <c r="P32">
-        <v>-0.7523183912</v>
+        <v>-0.7728610042399999</v>
       </c>
       <c r="Q32">
-        <v>-0.3023183912</v>
+        <v>-0.3228610042399999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1040584376205772</v>
+        <v>0.1049027628034842</v>
       </c>
       <c r="T32">
-        <v>0.8019493226134566</v>
+        <v>0.8135717765643763</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.05297865455971223</v>
+        <v>-0.05126966570294732</v>
       </c>
       <c r="W32">
-        <v>0.2482923667451802</v>
+        <v>0.247889387172755</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4042,7 +4053,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.220744393998801</v>
+        <v>-0.2136236070956137</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4050,22 +4061,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1492286163579581</v>
+        <v>0.1511286163579581</v>
       </c>
       <c r="C33">
-        <v>2.625487840972425</v>
+        <v>2.45008486094871</v>
       </c>
       <c r="D33">
-        <v>3.369017840972425</v>
+        <v>3.308244860948711</v>
       </c>
       <c r="E33">
-        <v>3.09053</v>
+        <v>3.20516</v>
       </c>
       <c r="F33">
-        <v>3.55353</v>
+        <v>3.66816</v>
       </c>
       <c r="G33">
         <v>2.81</v>
@@ -4086,37 +4097,37 @@
         <v>-0.179</v>
       </c>
       <c r="M33">
-        <v>0.837922374</v>
+        <v>0.864952128</v>
       </c>
       <c r="N33">
-        <v>-1.016922374</v>
+        <v>-1.043952128</v>
       </c>
       <c r="O33">
-        <v>-0.24406136976</v>
+        <v>-0.25054851072</v>
       </c>
       <c r="P33">
-        <v>-0.7728610042399999</v>
+        <v>-0.79340361728</v>
       </c>
       <c r="Q33">
-        <v>-0.3228610042399999</v>
+        <v>-0.34340361728</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1049027628034842</v>
+        <v>0.105771921080006</v>
       </c>
       <c r="T33">
-        <v>0.8135717765643763</v>
+        <v>0.8255360673962053</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.05126966570294732</v>
+        <v>-0.04966748864973022</v>
       </c>
       <c r="W33">
-        <v>0.247889387172755</v>
+        <v>0.2475115938236064</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4124,7 +4135,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.2136236070956137</v>
+        <v>-0.2069478693738758</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4132,22 +4143,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1511286163579581</v>
+        <v>0.1530286163579581</v>
       </c>
       <c r="C34">
-        <v>2.45008486094871</v>
+        <v>2.276835572093771</v>
       </c>
       <c r="D34">
-        <v>3.308244860948711</v>
+        <v>3.249625572093771</v>
       </c>
       <c r="E34">
-        <v>3.20516</v>
+        <v>3.31979</v>
       </c>
       <c r="F34">
-        <v>3.66816</v>
+        <v>3.78279</v>
       </c>
       <c r="G34">
         <v>2.81</v>
@@ -4168,37 +4179,37 @@
         <v>-0.179</v>
       </c>
       <c r="M34">
-        <v>0.864952128</v>
+        <v>0.8919818820000001</v>
       </c>
       <c r="N34">
-        <v>-1.043952128</v>
+        <v>-1.070981882</v>
       </c>
       <c r="O34">
-        <v>-0.25054851072</v>
+        <v>-0.25703565168</v>
       </c>
       <c r="P34">
-        <v>-0.79340361728</v>
+        <v>-0.81394623032</v>
       </c>
       <c r="Q34">
-        <v>-0.34340361728</v>
+        <v>-0.36394623032</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.105771921080006</v>
+        <v>0.1066670243797076</v>
       </c>
       <c r="T34">
-        <v>0.8255360673962053</v>
+        <v>0.8378575012379398</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.04966748864973022</v>
+        <v>-0.04816241323610203</v>
       </c>
       <c r="W34">
-        <v>0.2475115938236064</v>
+        <v>0.2471566970410729</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4206,7 +4217,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.2069478693738758</v>
+        <v>-0.2006767218170917</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4214,22 +4225,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1530286163579581</v>
+        <v>0.1549286163579581</v>
       </c>
       <c r="C35">
-        <v>2.276835572093771</v>
+        <v>2.105627482926713</v>
       </c>
       <c r="D35">
-        <v>3.249625572093771</v>
+        <v>3.193047482926713</v>
       </c>
       <c r="E35">
-        <v>3.31979</v>
+        <v>3.43442</v>
       </c>
       <c r="F35">
-        <v>3.78279</v>
+        <v>3.89742</v>
       </c>
       <c r="G35">
         <v>2.81</v>
@@ -4250,37 +4261,37 @@
         <v>-0.179</v>
       </c>
       <c r="M35">
-        <v>0.8919818820000001</v>
+        <v>0.919011636</v>
       </c>
       <c r="N35">
-        <v>-1.070981882</v>
+        <v>-1.098011636</v>
       </c>
       <c r="O35">
-        <v>-0.25703565168</v>
+        <v>-0.26352279264</v>
       </c>
       <c r="P35">
-        <v>-0.81394623032</v>
+        <v>-0.8344888433600001</v>
       </c>
       <c r="Q35">
-        <v>-0.36394623032</v>
+        <v>-0.3844888433600001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1066670243797076</v>
+        <v>0.1075892520218243</v>
       </c>
       <c r="T35">
-        <v>0.8378575012379398</v>
+        <v>0.850552311862757</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.04816241323610203</v>
+        <v>-0.04674587167033432</v>
       </c>
       <c r="W35">
-        <v>0.2471566970410729</v>
+        <v>0.2468226765398649</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4288,7 +4299,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.2006767218170917</v>
+        <v>-0.1947744652930596</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4296,22 +4307,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1549286163579581</v>
+        <v>0.1568286163579581</v>
       </c>
       <c r="C36">
-        <v>2.105627482926713</v>
+        <v>1.936355802100923</v>
       </c>
       <c r="D36">
-        <v>3.193047482926713</v>
+        <v>3.138405802100924</v>
       </c>
       <c r="E36">
-        <v>3.43442</v>
+        <v>3.54905</v>
       </c>
       <c r="F36">
-        <v>3.89742</v>
+        <v>4.01205</v>
       </c>
       <c r="G36">
         <v>2.81</v>
@@ -4332,37 +4343,37 @@
         <v>-0.179</v>
       </c>
       <c r="M36">
-        <v>0.919011636</v>
+        <v>0.9460413900000001</v>
       </c>
       <c r="N36">
-        <v>-1.098011636</v>
+        <v>-1.12504139</v>
       </c>
       <c r="O36">
-        <v>-0.26352279264</v>
+        <v>-0.2700099336</v>
       </c>
       <c r="P36">
-        <v>-0.8344888433600001</v>
+        <v>-0.8550314564000001</v>
       </c>
       <c r="Q36">
-        <v>-0.3844888433600001</v>
+        <v>-0.4050314564000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1075892520218243</v>
+        <v>0.1085398558990832</v>
       </c>
       <c r="T36">
-        <v>0.850552311862757</v>
+        <v>0.863637732045261</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.04674587167033432</v>
+        <v>-0.0454102753368962</v>
       </c>
       <c r="W36">
-        <v>0.2468226765398649</v>
+        <v>0.2465077429244401</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4370,7 +4381,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.1947744652930596</v>
+        <v>-0.1892094805704008</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4378,22 +4389,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1568286163579581</v>
+        <v>0.1587286163579581</v>
       </c>
       <c r="C37">
-        <v>1.936355802100923</v>
+        <v>1.768922790638438</v>
       </c>
       <c r="D37">
-        <v>3.138405802100924</v>
+        <v>3.085602790638439</v>
       </c>
       <c r="E37">
-        <v>3.54905</v>
+        <v>3.66368</v>
       </c>
       <c r="F37">
-        <v>4.01205</v>
+        <v>4.12668</v>
       </c>
       <c r="G37">
         <v>2.81</v>
@@ -4414,37 +4425,37 @@
         <v>-0.179</v>
       </c>
       <c r="M37">
-        <v>0.9460413900000001</v>
+        <v>0.9730711440000002</v>
       </c>
       <c r="N37">
-        <v>-1.12504139</v>
+        <v>-1.152071144</v>
       </c>
       <c r="O37">
-        <v>-0.2700099336</v>
+        <v>-0.2764970745600001</v>
       </c>
       <c r="P37">
-        <v>-0.8550314564000001</v>
+        <v>-0.8755740694400002</v>
       </c>
       <c r="Q37">
-        <v>-0.4050314564000001</v>
+        <v>-0.4255740694400001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1085398558990832</v>
+        <v>0.1095201661475063</v>
       </c>
       <c r="T37">
-        <v>0.863637732045261</v>
+        <v>0.8771320716084682</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.0454102753368962</v>
+        <v>-0.04414887879976018</v>
       </c>
       <c r="W37">
-        <v>0.2465077429244401</v>
+        <v>0.2462103056209834</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4452,7 +4463,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.1892094805704008</v>
+        <v>-0.1839536616656674</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4460,22 +4471,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1587286163579581</v>
+        <v>0.1606286163579581</v>
       </c>
       <c r="C38">
-        <v>1.768922790638439</v>
+        <v>1.603237178473461</v>
       </c>
       <c r="D38">
-        <v>3.085602790638439</v>
+        <v>3.03454717847346</v>
       </c>
       <c r="E38">
-        <v>3.663679999999999</v>
+        <v>3.778309999999999</v>
       </c>
       <c r="F38">
-        <v>4.126679999999999</v>
+        <v>4.241309999999999</v>
       </c>
       <c r="G38">
         <v>2.81</v>
@@ -4496,37 +4507,37 @@
         <v>-0.179</v>
       </c>
       <c r="M38">
-        <v>0.9730711439999999</v>
+        <v>1.000100898</v>
       </c>
       <c r="N38">
-        <v>-1.152071144</v>
+        <v>-1.179100898</v>
       </c>
       <c r="O38">
-        <v>-0.27649707456</v>
+        <v>-0.28298421552</v>
       </c>
       <c r="P38">
-        <v>-0.87557406944</v>
+        <v>-0.89611668248</v>
       </c>
       <c r="Q38">
-        <v>-0.42557406944</v>
+        <v>-0.44611668248</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1095201661475063</v>
+        <v>0.1105315973561969</v>
       </c>
       <c r="T38">
-        <v>0.8771320716084681</v>
+        <v>0.8910548029038406</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.04414887879976019</v>
+        <v>-0.04295566585922613</v>
       </c>
       <c r="W38">
-        <v>0.2462103056209834</v>
+        <v>0.2459289460096055</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4534,7 +4545,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.1839536616656676</v>
+        <v>-0.178981941080109</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4542,22 +4553,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1606286163579581</v>
+        <v>0.1625286163579581</v>
       </c>
       <c r="C39">
-        <v>1.603237178473461</v>
+        <v>1.439213637977626</v>
       </c>
       <c r="D39">
-        <v>3.03454717847346</v>
+        <v>2.985153637977626</v>
       </c>
       <c r="E39">
-        <v>3.778309999999999</v>
+        <v>3.892939999999999</v>
       </c>
       <c r="F39">
-        <v>4.241309999999999</v>
+        <v>4.355939999999999</v>
       </c>
       <c r="G39">
         <v>2.81</v>
@@ -4578,37 +4589,37 @@
         <v>-0.179</v>
       </c>
       <c r="M39">
-        <v>1.000100898</v>
+        <v>1.027130652</v>
       </c>
       <c r="N39">
-        <v>-1.179100898</v>
+        <v>-1.206130652</v>
       </c>
       <c r="O39">
-        <v>-0.28298421552</v>
+        <v>-0.2894713564799999</v>
       </c>
       <c r="P39">
-        <v>-0.89611668248</v>
+        <v>-0.9166592955199999</v>
       </c>
       <c r="Q39">
-        <v>-0.44611668248</v>
+        <v>-0.4666592955199999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1105315973561969</v>
+        <v>0.1115756553780711</v>
       </c>
       <c r="T39">
-        <v>0.8910548029038406</v>
+        <v>0.90542665456358</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.04295566585922613</v>
+        <v>-0.04182525359977281</v>
       </c>
       <c r="W39">
-        <v>0.2459289460096055</v>
+        <v>0.2456623947988264</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4616,7 +4627,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.178981941080109</v>
+        <v>-0.1742718899990534</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4624,22 +4635,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1625286163579581</v>
+        <v>0.1644286163579581</v>
       </c>
       <c r="C40">
-        <v>1.439213637977626</v>
+        <v>1.276772308078582</v>
       </c>
       <c r="D40">
-        <v>2.985153637977626</v>
+        <v>2.937342308078582</v>
       </c>
       <c r="E40">
-        <v>3.892939999999999</v>
+        <v>4.007569999999999</v>
       </c>
       <c r="F40">
-        <v>4.355939999999999</v>
+        <v>4.470569999999999</v>
       </c>
       <c r="G40">
         <v>2.81</v>
@@ -4660,37 +4671,37 @@
         <v>-0.179</v>
       </c>
       <c r="M40">
-        <v>1.027130652</v>
+        <v>1.054160406</v>
       </c>
       <c r="N40">
-        <v>-1.206130652</v>
+        <v>-1.233160406</v>
       </c>
       <c r="O40">
-        <v>-0.2894713564799999</v>
+        <v>-0.29595849744</v>
       </c>
       <c r="P40">
-        <v>-0.9166592955199999</v>
+        <v>-0.9372019085599999</v>
       </c>
       <c r="Q40">
-        <v>-0.4666592955199999</v>
+        <v>-0.4872019085599998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1115756553780711</v>
+        <v>0.1126539448104985</v>
       </c>
       <c r="T40">
-        <v>0.90542665456358</v>
+        <v>0.9202697144744584</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.04182525359977281</v>
+        <v>-0.04075281119977864</v>
       </c>
       <c r="W40">
-        <v>0.2456623947988264</v>
+        <v>0.2454095128809078</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4698,7 +4709,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.1742718899990534</v>
+        <v>-0.1698033799990777</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4706,22 +4717,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1644286163579581</v>
+        <v>0.1663286163579581</v>
       </c>
       <c r="C41">
-        <v>1.276772308078582</v>
+        <v>1.115838363389012</v>
       </c>
       <c r="D41">
-        <v>2.937342308078582</v>
+        <v>2.891038363389011</v>
       </c>
       <c r="E41">
-        <v>4.007569999999999</v>
+        <v>4.122199999999999</v>
       </c>
       <c r="F41">
-        <v>4.470569999999999</v>
+        <v>4.585199999999999</v>
       </c>
       <c r="G41">
         <v>2.81</v>
@@ -4742,37 +4753,37 @@
         <v>-0.179</v>
       </c>
       <c r="M41">
-        <v>1.054160406</v>
+        <v>1.08119016</v>
       </c>
       <c r="N41">
-        <v>-1.233160406</v>
+        <v>-1.26019016</v>
       </c>
       <c r="O41">
-        <v>-0.29595849744</v>
+        <v>-0.3024456384</v>
       </c>
       <c r="P41">
-        <v>-0.9372019085599999</v>
+        <v>-0.9577445216</v>
       </c>
       <c r="Q41">
-        <v>-0.4872019085599998</v>
+        <v>-0.5077445216000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1126539448104985</v>
+        <v>0.1137681772240068</v>
       </c>
       <c r="T41">
-        <v>0.9202697144744584</v>
+        <v>0.9356075430490327</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.04075281119977864</v>
+        <v>-0.03973399091978418</v>
       </c>
       <c r="W41">
-        <v>0.2454095128809078</v>
+        <v>0.2451692750588851</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4780,7 +4791,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.1698033799990777</v>
+        <v>-0.1655582954991008</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4788,22 +4799,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1663286163579581</v>
+        <v>0.1682286163579581</v>
       </c>
       <c r="C42">
-        <v>1.115838363389012</v>
+        <v>0.9563416234564226</v>
       </c>
       <c r="D42">
-        <v>2.891038363389011</v>
+        <v>2.846171623456423</v>
       </c>
       <c r="E42">
-        <v>4.122199999999999</v>
+        <v>4.23683</v>
       </c>
       <c r="F42">
-        <v>4.585199999999999</v>
+        <v>4.69983</v>
       </c>
       <c r="G42">
         <v>2.81</v>
@@ -4824,37 +4835,37 @@
         <v>-0.179</v>
       </c>
       <c r="M42">
-        <v>1.08119016</v>
+        <v>1.108219914</v>
       </c>
       <c r="N42">
-        <v>-1.26019016</v>
+        <v>-1.287219914</v>
       </c>
       <c r="O42">
-        <v>-0.3024456384</v>
+        <v>-0.30893277936</v>
       </c>
       <c r="P42">
-        <v>-0.9577445216</v>
+        <v>-0.9782871346400002</v>
       </c>
       <c r="Q42">
-        <v>-0.5077445216000001</v>
+        <v>-0.5282871346400002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1137681772240068</v>
+        <v>0.1149201802278035</v>
       </c>
       <c r="T42">
-        <v>0.9356075430490327</v>
+        <v>0.9514652980159655</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.03973399091978418</v>
+        <v>-0.03876486919003334</v>
       </c>
       <c r="W42">
-        <v>0.2451692750588851</v>
+        <v>0.2449407561550099</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4862,7 +4873,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.1655582954991008</v>
+        <v>-0.1615202882918056</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4870,22 +4881,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1682286163579581</v>
+        <v>0.1701286163579581</v>
       </c>
       <c r="C43">
-        <v>0.9563416234564226</v>
+        <v>0.7982161978417945</v>
       </c>
       <c r="D43">
-        <v>2.846171623456423</v>
+        <v>2.802676197841794</v>
       </c>
       <c r="E43">
-        <v>4.23683</v>
+        <v>4.35146</v>
       </c>
       <c r="F43">
-        <v>4.69983</v>
+        <v>4.81446</v>
       </c>
       <c r="G43">
         <v>2.81</v>
@@ -4906,37 +4917,37 @@
         <v>-0.179</v>
       </c>
       <c r="M43">
-        <v>1.108219914</v>
+        <v>1.135249668</v>
       </c>
       <c r="N43">
-        <v>-1.287219914</v>
+        <v>-1.314249668</v>
       </c>
       <c r="O43">
-        <v>-0.30893277936</v>
+        <v>-0.31541992032</v>
       </c>
       <c r="P43">
-        <v>-0.9782871346400002</v>
+        <v>-0.9988297476800001</v>
       </c>
       <c r="Q43">
-        <v>-0.5282871346400002</v>
+        <v>-0.5488297476800001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1149201802278035</v>
+        <v>0.1161119074731105</v>
       </c>
       <c r="T43">
-        <v>0.9514652980159655</v>
+        <v>0.9678698721196889</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.03876486919003334</v>
+        <v>-0.03784189611408016</v>
       </c>
       <c r="W43">
-        <v>0.2449407561550099</v>
+        <v>0.2447231191037001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4944,7 +4955,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.1615202882918056</v>
+        <v>-0.1576745671420008</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4952,22 +4963,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1701286163579581</v>
+        <v>0.1720286163579581</v>
       </c>
       <c r="C44">
-        <v>0.7982161978417954</v>
+        <v>0.641400163251995</v>
       </c>
       <c r="D44">
-        <v>2.802676197841794</v>
+        <v>2.760490163251995</v>
       </c>
       <c r="E44">
-        <v>4.351459999999999</v>
+        <v>4.466089999999999</v>
       </c>
       <c r="F44">
-        <v>4.81446</v>
+        <v>4.92909</v>
       </c>
       <c r="G44">
         <v>2.81</v>
@@ -4988,37 +4999,37 @@
         <v>-0.179</v>
       </c>
       <c r="M44">
-        <v>1.135249668</v>
+        <v>1.162279422</v>
       </c>
       <c r="N44">
-        <v>-1.314249668</v>
+        <v>-1.341279422</v>
       </c>
       <c r="O44">
-        <v>-0.31541992032</v>
+        <v>-0.32190706128</v>
       </c>
       <c r="P44">
-        <v>-0.99882974768</v>
+        <v>-1.01937236072</v>
       </c>
       <c r="Q44">
-        <v>-0.5488297476799999</v>
+        <v>-0.5693723607200001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1161119074731105</v>
+        <v>0.1173454497094808</v>
       </c>
       <c r="T44">
-        <v>0.9678698721196889</v>
+        <v>0.9848500453147712</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.03784189611408017</v>
+        <v>-0.03696185201840389</v>
       </c>
       <c r="W44">
-        <v>0.2447231191037001</v>
+        <v>0.2445156047059396</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5026,7 +5037,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.1576745671420008</v>
+        <v>-0.1540077167433496</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5034,22 +5045,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1720286163579581</v>
+        <v>0.1739286163579581</v>
       </c>
       <c r="C45">
-        <v>0.641400163251995</v>
+        <v>0.4858352693987298</v>
       </c>
       <c r="D45">
-        <v>2.760490163251995</v>
+        <v>2.719555269398729</v>
       </c>
       <c r="E45">
-        <v>4.466089999999999</v>
+        <v>4.580719999999999</v>
       </c>
       <c r="F45">
-        <v>4.92909</v>
+        <v>5.04372</v>
       </c>
       <c r="G45">
         <v>2.81</v>
@@ -5070,37 +5081,37 @@
         <v>-0.179</v>
       </c>
       <c r="M45">
-        <v>1.162279422</v>
+        <v>1.189309176</v>
       </c>
       <c r="N45">
-        <v>-1.341279422</v>
+        <v>-1.368309176</v>
       </c>
       <c r="O45">
-        <v>-0.32190706128</v>
+        <v>-0.32839420224</v>
       </c>
       <c r="P45">
-        <v>-1.01937236072</v>
+        <v>-1.03991497376</v>
       </c>
       <c r="Q45">
-        <v>-0.5693723607200001</v>
+        <v>-0.58991497376</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1173454497094808</v>
+        <v>0.1186230470257215</v>
       </c>
       <c r="T45">
-        <v>0.9848500453147712</v>
+        <v>1.002436653266821</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.03696185201840389</v>
+        <v>-0.03612180992707652</v>
       </c>
       <c r="W45">
-        <v>0.2445156047059396</v>
+        <v>0.2443175227808047</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5108,7 +5119,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.1540077167433496</v>
+        <v>-0.150507541362819</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5116,22 +5127,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1739286163579581</v>
+        <v>0.1758286163579581</v>
       </c>
       <c r="C46">
-        <v>0.4858352693987298</v>
+        <v>0.3314666706457228</v>
       </c>
       <c r="D46">
-        <v>2.719555269398729</v>
+        <v>2.679816670645722</v>
       </c>
       <c r="E46">
-        <v>4.580719999999999</v>
+        <v>4.695349999999999</v>
       </c>
       <c r="F46">
-        <v>5.04372</v>
+        <v>5.15835</v>
       </c>
       <c r="G46">
         <v>2.81</v>
@@ -5152,37 +5163,37 @@
         <v>-0.179</v>
       </c>
       <c r="M46">
-        <v>1.189309176</v>
+        <v>1.21633893</v>
       </c>
       <c r="N46">
-        <v>-1.368309176</v>
+        <v>-1.39533893</v>
       </c>
       <c r="O46">
-        <v>-0.32839420224</v>
+        <v>-0.3348813432</v>
       </c>
       <c r="P46">
-        <v>-1.03991497376</v>
+        <v>-1.0604575868</v>
       </c>
       <c r="Q46">
-        <v>-0.58991497376</v>
+        <v>-0.6104575868000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1186230470257215</v>
+        <v>0.1199471024261892</v>
       </c>
       <c r="T46">
-        <v>1.002436653266821</v>
+        <v>1.020662774235308</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.03612180992707652</v>
+        <v>-0.03531910303980815</v>
       </c>
       <c r="W46">
-        <v>0.2443175227808047</v>
+        <v>0.2441282444967868</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5190,7 +5201,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.150507541362819</v>
+        <v>-0.1471629293325341</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5198,22 +5209,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1758286163579581</v>
+        <v>0.1777286163579581</v>
       </c>
       <c r="C47">
-        <v>0.3314666706457228</v>
+        <v>0.1782426808443605</v>
       </c>
       <c r="D47">
-        <v>2.679816670645722</v>
+        <v>2.64122268084436</v>
       </c>
       <c r="E47">
-        <v>4.695349999999999</v>
+        <v>4.809979999999999</v>
       </c>
       <c r="F47">
-        <v>5.15835</v>
+        <v>5.27298</v>
       </c>
       <c r="G47">
         <v>2.81</v>
@@ -5234,37 +5245,37 @@
         <v>-0.179</v>
       </c>
       <c r="M47">
-        <v>1.21633893</v>
+        <v>1.243368684</v>
       </c>
       <c r="N47">
-        <v>-1.39533893</v>
+        <v>-1.422368684</v>
       </c>
       <c r="O47">
-        <v>-0.3348813432</v>
+        <v>-0.34136848416</v>
       </c>
       <c r="P47">
-        <v>-1.0604575868</v>
+        <v>-1.08100019984</v>
       </c>
       <c r="Q47">
-        <v>-0.6104575868000002</v>
+        <v>-0.6310001998400001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1199471024261892</v>
+        <v>0.1213201969155631</v>
       </c>
       <c r="T47">
-        <v>1.020662774235308</v>
+        <v>1.039563936721148</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.03531910303980815</v>
+        <v>-0.03455129645198624</v>
       </c>
       <c r="W47">
-        <v>0.2441282444967868</v>
+        <v>0.2439471957033784</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5272,7 +5283,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.1471629293325341</v>
+        <v>-0.1439637352166094</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5280,22 +5291,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1777286163579581</v>
+        <v>0.1796286163579581</v>
       </c>
       <c r="C48">
-        <v>0.1782426808443605</v>
+        <v>0.02611454905331279</v>
       </c>
       <c r="D48">
-        <v>2.64122268084436</v>
+        <v>2.603724549053312</v>
       </c>
       <c r="E48">
-        <v>4.809979999999999</v>
+        <v>4.924609999999999</v>
       </c>
       <c r="F48">
-        <v>5.27298</v>
+        <v>5.38761</v>
       </c>
       <c r="G48">
         <v>2.81</v>
@@ -5316,37 +5327,37 @@
         <v>-0.179</v>
       </c>
       <c r="M48">
-        <v>1.243368684</v>
+        <v>1.270398438</v>
       </c>
       <c r="N48">
-        <v>-1.422368684</v>
+        <v>-1.449398438</v>
       </c>
       <c r="O48">
-        <v>-0.34136848416</v>
+        <v>-0.34785562512</v>
       </c>
       <c r="P48">
-        <v>-1.08100019984</v>
+        <v>-1.10154281288</v>
       </c>
       <c r="Q48">
-        <v>-0.6310001998400001</v>
+        <v>-0.65154281288</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1213201969155631</v>
+        <v>0.1227451062913284</v>
       </c>
       <c r="T48">
-        <v>1.039563936721148</v>
+        <v>1.059178350621546</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.03455129645198624</v>
+        <v>-0.0338161624849227</v>
       </c>
       <c r="W48">
-        <v>0.2439471957033784</v>
+        <v>0.2437738511139448</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5354,7 +5365,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.1439637352166094</v>
+        <v>-0.1409006770205112</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5362,22 +5373,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1796286163579581</v>
+        <v>0.1815286163579581</v>
       </c>
       <c r="C49">
-        <v>0.02611454905331279</v>
+        <v>-0.1249637459042852</v>
       </c>
       <c r="D49">
-        <v>2.603724549053312</v>
+        <v>2.567276254095715</v>
       </c>
       <c r="E49">
-        <v>4.924609999999999</v>
+        <v>5.03924</v>
       </c>
       <c r="F49">
-        <v>5.38761</v>
+        <v>5.50224</v>
       </c>
       <c r="G49">
         <v>2.81</v>
@@ -5398,37 +5409,37 @@
         <v>-0.179</v>
       </c>
       <c r="M49">
-        <v>1.270398438</v>
+        <v>1.297428192</v>
       </c>
       <c r="N49">
-        <v>-1.449398438</v>
+        <v>-1.476428192</v>
       </c>
       <c r="O49">
-        <v>-0.34785562512</v>
+        <v>-0.35434276608</v>
       </c>
       <c r="P49">
-        <v>-1.10154281288</v>
+        <v>-1.12208542592</v>
       </c>
       <c r="Q49">
-        <v>-0.65154281288</v>
+        <v>-0.6720854259200002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1227451062913284</v>
+        <v>0.124224819873854</v>
       </c>
       <c r="T49">
-        <v>1.059178350621546</v>
+        <v>1.079547165056576</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.0338161624849227</v>
+        <v>-0.03311165909982014</v>
       </c>
       <c r="W49">
-        <v>0.2437738511139448</v>
+        <v>0.2436077292157376</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5436,7 +5447,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.1409006770205112</v>
+        <v>-0.1379652462492507</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5444,22 +5455,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1815286163579581</v>
+        <v>0.1834286163579581</v>
       </c>
       <c r="C50">
-        <v>-0.1249637459042843</v>
+        <v>-0.2750356838664816</v>
       </c>
       <c r="D50">
-        <v>2.567276254095715</v>
+        <v>2.531834316133518</v>
       </c>
       <c r="E50">
-        <v>5.039239999999999</v>
+        <v>5.15387</v>
       </c>
       <c r="F50">
-        <v>5.50224</v>
+        <v>5.61687</v>
       </c>
       <c r="G50">
         <v>2.81</v>
@@ -5480,37 +5491,37 @@
         <v>-0.179</v>
       </c>
       <c r="M50">
-        <v>1.297428192</v>
+        <v>1.324457946</v>
       </c>
       <c r="N50">
-        <v>-1.476428192</v>
+        <v>-1.503457946</v>
       </c>
       <c r="O50">
-        <v>-0.35434276608</v>
+        <v>-0.36082990704</v>
       </c>
       <c r="P50">
-        <v>-1.12208542592</v>
+        <v>-1.14262803896</v>
       </c>
       <c r="Q50">
-        <v>-0.67208542592</v>
+        <v>-0.6926280389599999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.124224819873854</v>
+        <v>0.125762561440008</v>
       </c>
       <c r="T50">
-        <v>1.079547165056576</v>
+        <v>1.100714756528274</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.03311165909982015</v>
+        <v>-0.03243591095492586</v>
       </c>
       <c r="W50">
-        <v>0.2436077292157376</v>
+        <v>0.2434483878031715</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5518,7 +5529,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.1379652462492507</v>
+        <v>-0.1351496289788578</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5526,22 +5537,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1834286163579581</v>
+        <v>0.1853286163579581</v>
       </c>
       <c r="C51">
-        <v>-0.2750356838664816</v>
+        <v>-0.424142376363112</v>
       </c>
       <c r="D51">
-        <v>2.531834316133518</v>
+        <v>2.497357623636888</v>
       </c>
       <c r="E51">
-        <v>5.15387</v>
+        <v>5.2685</v>
       </c>
       <c r="F51">
-        <v>5.61687</v>
+        <v>5.7315</v>
       </c>
       <c r="G51">
         <v>2.81</v>
@@ -5562,37 +5573,37 @@
         <v>-0.179</v>
       </c>
       <c r="M51">
-        <v>1.324457946</v>
+        <v>1.3514877</v>
       </c>
       <c r="N51">
-        <v>-1.503457946</v>
+        <v>-1.5304877</v>
       </c>
       <c r="O51">
-        <v>-0.36082990704</v>
+        <v>-0.367317048</v>
       </c>
       <c r="P51">
-        <v>-1.14262803896</v>
+        <v>-1.163170652</v>
       </c>
       <c r="Q51">
-        <v>-0.6926280389599999</v>
+        <v>-0.7131706520000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.125762561440008</v>
+        <v>0.1273618126688081</v>
       </c>
       <c r="T51">
-        <v>1.100714756528274</v>
+        <v>1.122729051658839</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.03243591095492586</v>
+        <v>-0.03178719273582734</v>
       </c>
       <c r="W51">
-        <v>0.2434483878031715</v>
+        <v>0.2432954200471081</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5600,7 +5611,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.1351496289788578</v>
+        <v>-0.1324466363992807</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5608,22 +5619,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1853286163579581</v>
+        <v>0.1872286163579581</v>
       </c>
       <c r="C52">
-        <v>-0.424142376363112</v>
+        <v>-0.5723227256990668</v>
       </c>
       <c r="D52">
-        <v>2.497357623636888</v>
+        <v>2.463807274300933</v>
       </c>
       <c r="E52">
-        <v>5.2685</v>
+        <v>5.38313</v>
       </c>
       <c r="F52">
-        <v>5.7315</v>
+        <v>5.84613</v>
       </c>
       <c r="G52">
         <v>2.81</v>
@@ -5644,37 +5655,37 @@
         <v>-0.179</v>
       </c>
       <c r="M52">
-        <v>1.3514877</v>
+        <v>1.378517454</v>
       </c>
       <c r="N52">
-        <v>-1.5304877</v>
+        <v>-1.557517454</v>
       </c>
       <c r="O52">
-        <v>-0.367317048</v>
+        <v>-0.37380418896</v>
       </c>
       <c r="P52">
-        <v>-1.163170652</v>
+        <v>-1.18371326504</v>
       </c>
       <c r="Q52">
-        <v>-0.7131706520000001</v>
+        <v>-0.7337132650400002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1273618126688081</v>
+        <v>0.1290263394579675</v>
       </c>
       <c r="T52">
-        <v>1.122729051658839</v>
+        <v>1.145641889447795</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.03178719273582734</v>
+        <v>-0.03116391444688955</v>
       </c>
       <c r="W52">
-        <v>0.2432954200471081</v>
+        <v>0.2431484510265766</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5682,7 +5693,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.1324466363992807</v>
+        <v>-0.1298496435287064</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5690,22 +5701,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1872286163579581</v>
+        <v>0.1891286163579581</v>
       </c>
       <c r="C53">
-        <v>-0.5723227256990668</v>
+        <v>-0.7196135713844836</v>
       </c>
       <c r="D53">
-        <v>2.463807274300933</v>
+        <v>2.431146428615516</v>
       </c>
       <c r="E53">
-        <v>5.38313</v>
+        <v>5.49776</v>
       </c>
       <c r="F53">
-        <v>5.84613</v>
+        <v>5.96076</v>
       </c>
       <c r="G53">
         <v>2.81</v>
@@ -5726,37 +5737,37 @@
         <v>-0.179</v>
       </c>
       <c r="M53">
-        <v>1.378517454</v>
+        <v>1.405547208</v>
       </c>
       <c r="N53">
-        <v>-1.557517454</v>
+        <v>-1.584547208</v>
       </c>
       <c r="O53">
-        <v>-0.37380418896</v>
+        <v>-0.38029132992</v>
       </c>
       <c r="P53">
-        <v>-1.18371326504</v>
+        <v>-1.20425587808</v>
       </c>
       <c r="Q53">
-        <v>-0.7337132650400002</v>
+        <v>-0.7542558780800002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1290263394579675</v>
+        <v>0.1307602215300085</v>
       </c>
       <c r="T53">
-        <v>1.145641889447795</v>
+        <v>1.169509428811291</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.03116391444688955</v>
+        <v>-0.03056460839983398</v>
       </c>
       <c r="W53">
-        <v>0.2431484510265766</v>
+        <v>0.2430071346606808</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5764,7 +5775,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.1298496435287064</v>
+        <v>-0.1273525349993083</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5772,22 +5783,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1891286163579581</v>
+        <v>0.1910286163579581</v>
       </c>
       <c r="C54">
-        <v>-0.7196135713844836</v>
+        <v>-0.8660498250706326</v>
       </c>
       <c r="D54">
-        <v>2.431146428615516</v>
+        <v>2.399340174929367</v>
       </c>
       <c r="E54">
-        <v>5.49776</v>
+        <v>5.61239</v>
       </c>
       <c r="F54">
-        <v>5.96076</v>
+        <v>6.07539</v>
       </c>
       <c r="G54">
         <v>2.81</v>
@@ -5808,37 +5819,37 @@
         <v>-0.179</v>
       </c>
       <c r="M54">
-        <v>1.405547208</v>
+        <v>1.432576962</v>
       </c>
       <c r="N54">
-        <v>-1.584547208</v>
+        <v>-1.611576962</v>
       </c>
       <c r="O54">
-        <v>-0.38029132992</v>
+        <v>-0.38677847088</v>
       </c>
       <c r="P54">
-        <v>-1.20425587808</v>
+        <v>-1.22479849112</v>
       </c>
       <c r="Q54">
-        <v>-0.7542558780800002</v>
+        <v>-0.7747984911200001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1307602215300085</v>
+        <v>0.132567885817881</v>
       </c>
       <c r="T54">
-        <v>1.169509428811291</v>
+        <v>1.194392608147701</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.03056460839983398</v>
+        <v>-0.02998791767530881</v>
       </c>
       <c r="W54">
-        <v>0.2430071346606808</v>
+        <v>0.2428711509878378</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5846,7 +5857,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.1273525349993083</v>
+        <v>-0.1249496569804533</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5854,22 +5865,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1910286163579581</v>
+        <v>0.1929286163579581</v>
       </c>
       <c r="C55">
-        <v>-0.8660498250706326</v>
+        <v>-1.011664595030505</v>
       </c>
       <c r="D55">
-        <v>2.399340174929367</v>
+        <v>2.368355404969494</v>
       </c>
       <c r="E55">
-        <v>5.61239</v>
+        <v>5.72702</v>
       </c>
       <c r="F55">
-        <v>6.07539</v>
+        <v>6.19002</v>
       </c>
       <c r="G55">
         <v>2.81</v>
@@ -5890,37 +5901,37 @@
         <v>-0.179</v>
       </c>
       <c r="M55">
-        <v>1.432576962</v>
+        <v>1.459606716</v>
       </c>
       <c r="N55">
-        <v>-1.611576962</v>
+        <v>-1.638606716</v>
       </c>
       <c r="O55">
-        <v>-0.38677847088</v>
+        <v>-0.39326561184</v>
       </c>
       <c r="P55">
-        <v>-1.22479849112</v>
+        <v>-1.24534110416</v>
       </c>
       <c r="Q55">
-        <v>-0.7747984911200001</v>
+        <v>-0.79534110416</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.132567885817881</v>
+        <v>0.1344541442052262</v>
       </c>
       <c r="T55">
-        <v>1.194392608147701</v>
+        <v>1.220357664846564</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.02998791767530881</v>
+        <v>-0.0294325858665068</v>
       </c>
       <c r="W55">
-        <v>0.2428711509878378</v>
+        <v>0.2427402037473223</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5928,7 +5939,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.1249496569804533</v>
+        <v>-0.1226357744437783</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5936,22 +5947,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1929286163579581</v>
+        <v>0.1948286163579581</v>
       </c>
       <c r="C56">
-        <v>-1.011664595030505</v>
+        <v>-1.156489301117245</v>
       </c>
       <c r="D56">
-        <v>2.368355404969494</v>
+        <v>2.338160698882755</v>
       </c>
       <c r="E56">
-        <v>5.72702</v>
+        <v>5.84165</v>
       </c>
       <c r="F56">
-        <v>6.19002</v>
+        <v>6.30465</v>
       </c>
       <c r="G56">
         <v>2.81</v>
@@ -5972,37 +5983,37 @@
         <v>-0.179</v>
       </c>
       <c r="M56">
-        <v>1.459606716</v>
+        <v>1.48663647</v>
       </c>
       <c r="N56">
-        <v>-1.638606716</v>
+        <v>-1.66563647</v>
       </c>
       <c r="O56">
-        <v>-0.39326561184</v>
+        <v>-0.3997527527999999</v>
       </c>
       <c r="P56">
-        <v>-1.24534110416</v>
+        <v>-1.2658837172</v>
       </c>
       <c r="Q56">
-        <v>-0.79534110416</v>
+        <v>-0.8158837172</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1344541442052262</v>
+        <v>0.1364242362986757</v>
       </c>
       <c r="T56">
-        <v>1.220357664846564</v>
+        <v>1.247476724065377</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.0294325858665068</v>
+        <v>-0.02889744794166122</v>
       </c>
       <c r="W56">
-        <v>0.2427402037473223</v>
+        <v>0.2426140182246437</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6010,7 +6021,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.1226357744437783</v>
+        <v>-0.1204060330902552</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6018,22 +6029,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1948286163579581</v>
+        <v>0.1967286163579581</v>
       </c>
       <c r="C57">
-        <v>-1.156489301117245</v>
+        <v>-1.300553781039469</v>
       </c>
       <c r="D57">
-        <v>2.338160698882755</v>
+        <v>2.308726218960532</v>
       </c>
       <c r="E57">
-        <v>5.84165</v>
+        <v>5.95628</v>
       </c>
       <c r="F57">
-        <v>6.30465</v>
+        <v>6.419280000000001</v>
       </c>
       <c r="G57">
         <v>2.81</v>
@@ -6054,37 +6065,37 @@
         <v>-0.179</v>
       </c>
       <c r="M57">
-        <v>1.48663647</v>
+        <v>1.513666224</v>
       </c>
       <c r="N57">
-        <v>-1.66563647</v>
+        <v>-1.692666224</v>
       </c>
       <c r="O57">
-        <v>-0.3997527527999999</v>
+        <v>-0.4062398937600001</v>
       </c>
       <c r="P57">
-        <v>-1.2658837172</v>
+        <v>-1.28642633024</v>
       </c>
       <c r="Q57">
-        <v>-0.8158837172</v>
+        <v>-0.8364263302400003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1364242362986757</v>
+        <v>0.1384838780327365</v>
       </c>
       <c r="T57">
-        <v>1.247476724065377</v>
+        <v>1.275828467794136</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.02889744794166122</v>
+        <v>-0.02838142208556012</v>
       </c>
       <c r="W57">
-        <v>0.2426140182246437</v>
+        <v>0.2424923393277751</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6092,7 +6103,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.1204060330902552</v>
+        <v>-0.1182559253565005</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6100,22 +6111,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1967286163579581</v>
+        <v>0.1986286163579581</v>
       </c>
       <c r="C58">
-        <v>-1.300553781039469</v>
+        <v>-1.443886388709165</v>
       </c>
       <c r="D58">
-        <v>2.308726218960532</v>
+        <v>2.280023611290835</v>
       </c>
       <c r="E58">
-        <v>5.95628</v>
+        <v>6.07091</v>
       </c>
       <c r="F58">
-        <v>6.419280000000001</v>
+        <v>6.533910000000001</v>
       </c>
       <c r="G58">
         <v>2.81</v>
@@ -6136,37 +6147,37 @@
         <v>-0.179</v>
       </c>
       <c r="M58">
-        <v>1.513666224</v>
+        <v>1.540695978</v>
       </c>
       <c r="N58">
-        <v>-1.692666224</v>
+        <v>-1.719695978</v>
       </c>
       <c r="O58">
-        <v>-0.4062398937600001</v>
+        <v>-0.4127270347200001</v>
       </c>
       <c r="P58">
-        <v>-1.28642633024</v>
+        <v>-1.30696894328</v>
       </c>
       <c r="Q58">
-        <v>-0.8364263302400003</v>
+        <v>-0.8569689432800003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1384838780327365</v>
+        <v>0.1406393170567536</v>
       </c>
       <c r="T58">
-        <v>1.275828467794136</v>
+        <v>1.30549889727772</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.02838142208556012</v>
+        <v>-0.02788350239984854</v>
       </c>
       <c r="W58">
-        <v>0.2424923393277751</v>
+        <v>0.2423749298658843</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6174,7 +6185,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.1182559253565005</v>
+        <v>-0.116181259999369</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6182,22 +6193,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1986286163579581</v>
+        <v>0.2005286163579581</v>
       </c>
       <c r="C59">
-        <v>-1.443886388709165</v>
+        <v>-1.586514085343579</v>
       </c>
       <c r="D59">
-        <v>2.280023611290835</v>
+        <v>2.252025914656421</v>
       </c>
       <c r="E59">
-        <v>6.07091</v>
+        <v>6.18554</v>
       </c>
       <c r="F59">
-        <v>6.533910000000001</v>
+        <v>6.648540000000001</v>
       </c>
       <c r="G59">
         <v>2.81</v>
@@ -6218,37 +6229,37 @@
         <v>-0.179</v>
       </c>
       <c r="M59">
-        <v>1.540695978</v>
+        <v>1.567725732</v>
       </c>
       <c r="N59">
-        <v>-1.719695978</v>
+        <v>-1.746725732</v>
       </c>
       <c r="O59">
-        <v>-0.4127270347200001</v>
+        <v>-0.41921417568</v>
       </c>
       <c r="P59">
-        <v>-1.30696894328</v>
+        <v>-1.32751155632</v>
       </c>
       <c r="Q59">
-        <v>-0.8569689432800003</v>
+        <v>-0.8775115563200002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1406393170567536</v>
+        <v>0.1428973960342954</v>
       </c>
       <c r="T59">
-        <v>1.30549889727772</v>
+        <v>1.336582204355761</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.02788350239984854</v>
+        <v>-0.02740275235847184</v>
       </c>
       <c r="W59">
-        <v>0.2423749298658843</v>
+        <v>0.2422615690061277</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6256,7 +6267,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.116181259999369</v>
+        <v>-0.1141781348269659</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6264,22 +6275,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2005286163579581</v>
+        <v>0.2024286163579581</v>
       </c>
       <c r="C60">
-        <v>-1.586514085343577</v>
+        <v>-1.728462523936359</v>
       </c>
       <c r="D60">
-        <v>2.252025914656421</v>
+        <v>2.22470747606364</v>
       </c>
       <c r="E60">
-        <v>6.185539999999999</v>
+        <v>6.300169999999999</v>
       </c>
       <c r="F60">
-        <v>6.648539999999999</v>
+        <v>6.763169999999999</v>
       </c>
       <c r="G60">
         <v>2.81</v>
@@ -6300,37 +6311,37 @@
         <v>-0.179</v>
       </c>
       <c r="M60">
-        <v>1.567725732</v>
+        <v>1.594755486</v>
       </c>
       <c r="N60">
-        <v>-1.746725732</v>
+        <v>-1.773755486</v>
       </c>
       <c r="O60">
-        <v>-0.4192141756799999</v>
+        <v>-0.4257013166399999</v>
       </c>
       <c r="P60">
-        <v>-1.32751155632</v>
+        <v>-1.34805416936</v>
       </c>
       <c r="Q60">
-        <v>-0.87751155632</v>
+        <v>-0.8980541693599999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1428973960342954</v>
+        <v>0.1452656252058635</v>
       </c>
       <c r="T60">
-        <v>1.336582204355761</v>
+        <v>1.369181770315657</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.02740275235847185</v>
+        <v>-0.02693829892866724</v>
       </c>
       <c r="W60">
-        <v>0.2422615690061277</v>
+        <v>0.2421520508873798</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6338,7 +6349,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.1141781348269661</v>
+        <v>-0.1122429122027802</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6346,22 +6357,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2024286163579581</v>
+        <v>0.2043286163579581</v>
       </c>
       <c r="C61">
-        <v>-1.728462523936359</v>
+        <v>-1.869756127654292</v>
       </c>
       <c r="D61">
-        <v>2.22470747606364</v>
+        <v>2.198043872345708</v>
       </c>
       <c r="E61">
-        <v>6.300169999999999</v>
+        <v>6.4148</v>
       </c>
       <c r="F61">
-        <v>6.763169999999999</v>
+        <v>6.8778</v>
       </c>
       <c r="G61">
         <v>2.81</v>
@@ -6382,37 +6393,37 @@
         <v>-0.179</v>
       </c>
       <c r="M61">
-        <v>1.594755486</v>
+        <v>1.62178524</v>
       </c>
       <c r="N61">
-        <v>-1.773755486</v>
+        <v>-1.80078524</v>
       </c>
       <c r="O61">
-        <v>-0.4257013166399999</v>
+        <v>-0.4321884576</v>
       </c>
       <c r="P61">
-        <v>-1.34805416936</v>
+        <v>-1.3685967824</v>
       </c>
       <c r="Q61">
-        <v>-0.8980541693599999</v>
+        <v>-0.9185967824000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1452656252058635</v>
+        <v>0.1477522658360101</v>
       </c>
       <c r="T61">
-        <v>1.369181770315657</v>
+        <v>1.403411314573549</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.02693829892866724</v>
+        <v>-0.02648932727985611</v>
       </c>
       <c r="W61">
-        <v>0.2421520508873798</v>
+        <v>0.2420461833725901</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6420,7 +6431,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.1122429122027802</v>
+        <v>-0.1103721969994005</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6428,22 +6439,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2043286163579581</v>
+        <v>0.2062286163579581</v>
       </c>
       <c r="C62">
-        <v>-1.869756127654292</v>
+        <v>-2.010418162663174</v>
       </c>
       <c r="D62">
-        <v>2.198043872345708</v>
+        <v>2.172011837336825</v>
       </c>
       <c r="E62">
-        <v>6.4148</v>
+        <v>6.52943</v>
       </c>
       <c r="F62">
-        <v>6.8778</v>
+        <v>6.99243</v>
       </c>
       <c r="G62">
         <v>2.81</v>
@@ -6464,37 +6475,37 @@
         <v>-0.179</v>
       </c>
       <c r="M62">
-        <v>1.62178524</v>
+        <v>1.648814994</v>
       </c>
       <c r="N62">
-        <v>-1.80078524</v>
+        <v>-1.827814994</v>
       </c>
       <c r="O62">
-        <v>-0.4321884576</v>
+        <v>-0.43867559856</v>
       </c>
       <c r="P62">
-        <v>-1.3685967824</v>
+        <v>-1.38913939544</v>
       </c>
       <c r="Q62">
-        <v>-0.9185967824000001</v>
+        <v>-0.9391393954400002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1477522658360101</v>
+        <v>0.150366426498472</v>
       </c>
       <c r="T62">
-        <v>1.403411314573549</v>
+        <v>1.439396220075435</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.02648932727985611</v>
+        <v>-0.02605507601297323</v>
       </c>
       <c r="W62">
-        <v>0.2420461833725901</v>
+        <v>0.2419437869238591</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6502,7 +6513,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.1103721969994005</v>
+        <v>-0.1085628167207218</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6510,22 +6521,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2062286163579581</v>
+        <v>0.2081286163579581</v>
       </c>
       <c r="C63">
-        <v>-2.010418162663174</v>
+        <v>-2.150470805839285</v>
       </c>
       <c r="D63">
-        <v>2.172011837336825</v>
+        <v>2.146589194160716</v>
       </c>
       <c r="E63">
-        <v>6.52943</v>
+        <v>6.64406</v>
       </c>
       <c r="F63">
-        <v>6.99243</v>
+        <v>7.10706</v>
       </c>
       <c r="G63">
         <v>2.81</v>
@@ -6546,37 +6557,37 @@
         <v>-0.179</v>
       </c>
       <c r="M63">
-        <v>1.648814994</v>
+        <v>1.675844748</v>
       </c>
       <c r="N63">
-        <v>-1.827814994</v>
+        <v>-1.854844748</v>
       </c>
       <c r="O63">
-        <v>-0.43867559856</v>
+        <v>-0.44516273952</v>
       </c>
       <c r="P63">
-        <v>-1.38913939544</v>
+        <v>-1.40968200848</v>
       </c>
       <c r="Q63">
-        <v>-0.9391393954400002</v>
+        <v>-0.9596820084800002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.150366426498472</v>
+        <v>0.1531181745642212</v>
       </c>
       <c r="T63">
-        <v>1.439396220075435</v>
+        <v>1.477275067972157</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.02605507601297323</v>
+        <v>-0.02563483285147366</v>
       </c>
       <c r="W63">
-        <v>0.2419437869238591</v>
+        <v>0.2418446935863775</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6584,7 +6595,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.1085628167207218</v>
+        <v>-0.1068118035478069</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6592,22 +6603,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2081286163579581</v>
+        <v>0.2100286163579581</v>
       </c>
       <c r="C64">
-        <v>-2.150470805839285</v>
+        <v>-2.289935207780634</v>
       </c>
       <c r="D64">
-        <v>2.146589194160716</v>
+        <v>2.121754792219365</v>
       </c>
       <c r="E64">
-        <v>6.64406</v>
+        <v>6.75869</v>
       </c>
       <c r="F64">
-        <v>7.10706</v>
+        <v>7.22169</v>
       </c>
       <c r="G64">
         <v>2.81</v>
@@ -6628,37 +6639,37 @@
         <v>-0.179</v>
       </c>
       <c r="M64">
-        <v>1.675844748</v>
+        <v>1.702874502</v>
       </c>
       <c r="N64">
-        <v>-1.854844748</v>
+        <v>-1.881874502</v>
       </c>
       <c r="O64">
-        <v>-0.44516273952</v>
+        <v>-0.45164988048</v>
       </c>
       <c r="P64">
-        <v>-1.40968200848</v>
+        <v>-1.43022462152</v>
       </c>
       <c r="Q64">
-        <v>-0.9596820084800002</v>
+        <v>-0.9802246215200001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1531181745642212</v>
+        <v>0.1560186657686596</v>
       </c>
       <c r="T64">
-        <v>1.477275067972157</v>
+        <v>1.517201421160594</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.02563483285147366</v>
+        <v>-0.02522793074272011</v>
       </c>
       <c r="W64">
-        <v>0.2418446935863775</v>
+        <v>0.2417487460691334</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6666,7 +6677,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.1068118035478069</v>
+        <v>-0.1051163780946671</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6674,22 +6685,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2100286163579581</v>
+        <v>0.2119286163579581</v>
       </c>
       <c r="C65">
-        <v>-2.289935207780634</v>
+        <v>-2.428831551494294</v>
       </c>
       <c r="D65">
-        <v>2.121754792219365</v>
+        <v>2.097488448505706</v>
       </c>
       <c r="E65">
-        <v>6.75869</v>
+        <v>6.87332</v>
       </c>
       <c r="F65">
-        <v>7.22169</v>
+        <v>7.33632</v>
       </c>
       <c r="G65">
         <v>2.81</v>
@@ -6710,37 +6721,37 @@
         <v>-0.179</v>
       </c>
       <c r="M65">
-        <v>1.702874502</v>
+        <v>1.729904256</v>
       </c>
       <c r="N65">
-        <v>-1.881874502</v>
+        <v>-1.908904256</v>
       </c>
       <c r="O65">
-        <v>-0.45164988048</v>
+        <v>-0.45813702144</v>
       </c>
       <c r="P65">
-        <v>-1.43022462152</v>
+        <v>-1.45076723456</v>
       </c>
       <c r="Q65">
-        <v>-0.9802246215200001</v>
+        <v>-1.00076723456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1560186657686596</v>
+        <v>0.1590802953733446</v>
       </c>
       <c r="T65">
-        <v>1.517201421160594</v>
+        <v>1.559345905081721</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.02522793074272011</v>
+        <v>-0.02483374432486511</v>
       </c>
       <c r="W65">
-        <v>0.2417487460691334</v>
+        <v>0.2416557969118032</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6748,7 +6759,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.1051163780946671</v>
+        <v>-0.103473934686938</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6756,22 +6767,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2119286163579581</v>
+        <v>0.2138286163579581</v>
       </c>
       <c r="C66">
-        <v>-2.428831551494294</v>
+        <v>-2.56717910710203</v>
       </c>
       <c r="D66">
-        <v>2.097488448505706</v>
+        <v>2.07377089289797</v>
       </c>
       <c r="E66">
-        <v>6.87332</v>
+        <v>6.98795</v>
       </c>
       <c r="F66">
-        <v>7.33632</v>
+        <v>7.45095</v>
       </c>
       <c r="G66">
         <v>2.81</v>
@@ -6792,37 +6803,37 @@
         <v>-0.179</v>
       </c>
       <c r="M66">
-        <v>1.729904256</v>
+        <v>1.75693401</v>
       </c>
       <c r="N66">
-        <v>-1.908904256</v>
+        <v>-1.93593401</v>
       </c>
       <c r="O66">
-        <v>-0.45813702144</v>
+        <v>-0.4646241624</v>
       </c>
       <c r="P66">
-        <v>-1.45076723456</v>
+        <v>-1.4713098476</v>
       </c>
       <c r="Q66">
-        <v>-1.00076723456</v>
+        <v>-1.0213098476</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1590802953733446</v>
+        <v>0.1623168752411545</v>
       </c>
       <c r="T66">
-        <v>1.559345905081721</v>
+        <v>1.603898645226913</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.02483374432486511</v>
+        <v>-0.02445168671986718</v>
       </c>
       <c r="W66">
-        <v>0.2416557969118032</v>
+        <v>0.2415657077285447</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6830,7 +6841,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.103473934686938</v>
+        <v>-0.1018820279994466</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6838,22 +6849,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2138286163579581</v>
+        <v>0.2157286163579581</v>
       </c>
       <c r="C67">
-        <v>-2.56717910710203</v>
+        <v>-2.704996282875921</v>
       </c>
       <c r="D67">
-        <v>2.07377089289797</v>
+        <v>2.050583717124078</v>
       </c>
       <c r="E67">
-        <v>6.98795</v>
+        <v>7.10258</v>
       </c>
       <c r="F67">
-        <v>7.45095</v>
+        <v>7.56558</v>
       </c>
       <c r="G67">
         <v>2.81</v>
@@ -6874,37 +6885,37 @@
         <v>-0.179</v>
       </c>
       <c r="M67">
-        <v>1.75693401</v>
+        <v>1.783963764</v>
       </c>
       <c r="N67">
-        <v>-1.93593401</v>
+        <v>-1.962963764</v>
       </c>
       <c r="O67">
-        <v>-0.4646241624</v>
+        <v>-0.47111130336</v>
       </c>
       <c r="P67">
-        <v>-1.4713098476</v>
+        <v>-1.49185246064</v>
       </c>
       <c r="Q67">
-        <v>-1.0213098476</v>
+        <v>-1.04185246064</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1623168752411545</v>
+        <v>0.165743842160012</v>
       </c>
       <c r="T67">
-        <v>1.603898645226913</v>
+        <v>1.651072134792411</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.02445168671986718</v>
+        <v>-0.02408120661805101</v>
       </c>
       <c r="W67">
-        <v>0.2415657077285447</v>
+        <v>0.2414783485205364</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6912,7 +6923,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.1018820279994466</v>
+        <v>-0.100338360908546</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6920,22 +6931,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2157286163579581</v>
+        <v>0.2176286163579581</v>
       </c>
       <c r="C68">
-        <v>-2.704996282875921</v>
+        <v>-2.842300672887998</v>
       </c>
       <c r="D68">
-        <v>2.050583717124078</v>
+        <v>2.027909327112002</v>
       </c>
       <c r="E68">
-        <v>7.10258</v>
+        <v>7.21721</v>
       </c>
       <c r="F68">
-        <v>7.56558</v>
+        <v>7.68021</v>
       </c>
       <c r="G68">
         <v>2.81</v>
@@ -6956,37 +6967,37 @@
         <v>-0.179</v>
       </c>
       <c r="M68">
-        <v>1.783963764</v>
+        <v>1.810993518</v>
       </c>
       <c r="N68">
-        <v>-1.962963764</v>
+        <v>-1.989993518</v>
       </c>
       <c r="O68">
-        <v>-0.47111130336</v>
+        <v>-0.47759844432</v>
       </c>
       <c r="P68">
-        <v>-1.49185246064</v>
+        <v>-1.51239507368</v>
       </c>
       <c r="Q68">
-        <v>-1.04185246064</v>
+        <v>-1.06239507368</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.165743842160012</v>
+        <v>0.1693785040436487</v>
       </c>
       <c r="T68">
-        <v>1.651072134792411</v>
+        <v>1.701104623725514</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.02408120661805101</v>
+        <v>-0.02372178562375174</v>
       </c>
       <c r="W68">
-        <v>0.2414783485205364</v>
+        <v>0.2413935970500807</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6994,7 +7005,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.100338360908546</v>
+        <v>-0.09884077343229891</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7002,22 +7013,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2176286163579581</v>
+        <v>0.2195286163579581</v>
       </c>
       <c r="C69">
-        <v>-2.842300672887998</v>
+        <v>-2.979109101533132</v>
       </c>
       <c r="D69">
-        <v>2.027909327112002</v>
+        <v>2.005730898466868</v>
       </c>
       <c r="E69">
-        <v>7.21721</v>
+        <v>7.33184</v>
       </c>
       <c r="F69">
-        <v>7.68021</v>
+        <v>7.79484</v>
       </c>
       <c r="G69">
         <v>2.81</v>
@@ -7038,37 +7049,37 @@
         <v>-0.179</v>
       </c>
       <c r="M69">
-        <v>1.810993518</v>
+        <v>1.838023272</v>
       </c>
       <c r="N69">
-        <v>-1.989993518</v>
+        <v>-2.017023272</v>
       </c>
       <c r="O69">
-        <v>-0.47759844432</v>
+        <v>-0.48408558528</v>
       </c>
       <c r="P69">
-        <v>-1.51239507368</v>
+        <v>-1.53293768672</v>
       </c>
       <c r="Q69">
-        <v>-1.06239507368</v>
+        <v>-1.08293768672</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1693785040436487</v>
+        <v>0.1732403322950127</v>
       </c>
       <c r="T69">
-        <v>1.701104623725514</v>
+        <v>1.754264143216936</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.02372178562375174</v>
+        <v>-0.02337293583516716</v>
       </c>
       <c r="W69">
-        <v>0.2413935970500807</v>
+        <v>0.2413113382699324</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7076,7 +7087,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.09884077343229891</v>
+        <v>-0.09738723264652971</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7084,22 +7095,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2195286163579581</v>
+        <v>0.2214286163579581</v>
       </c>
       <c r="C70">
-        <v>-2.979109101533132</v>
+        <v>-3.115437665161966</v>
       </c>
       <c r="D70">
-        <v>2.005730898466868</v>
+        <v>1.984032334838035</v>
       </c>
       <c r="E70">
-        <v>7.33184</v>
+        <v>7.44647</v>
       </c>
       <c r="F70">
-        <v>7.79484</v>
+        <v>7.90947</v>
       </c>
       <c r="G70">
         <v>2.81</v>
@@ -7120,37 +7131,37 @@
         <v>-0.179</v>
       </c>
       <c r="M70">
-        <v>1.838023272</v>
+        <v>1.865053026</v>
       </c>
       <c r="N70">
-        <v>-2.017023272</v>
+        <v>-2.044053026</v>
       </c>
       <c r="O70">
-        <v>-0.48408558528</v>
+        <v>-0.4905727262399999</v>
       </c>
       <c r="P70">
-        <v>-1.53293768672</v>
+        <v>-1.55348029976</v>
       </c>
       <c r="Q70">
-        <v>-1.08293768672</v>
+        <v>-1.10348029976</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1732403322950127</v>
+        <v>0.1773513107561422</v>
       </c>
       <c r="T70">
-        <v>1.754264143216936</v>
+        <v>1.81085330912716</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.02337293583516716</v>
+        <v>-0.02303419763465749</v>
       </c>
       <c r="W70">
-        <v>0.2413113382699324</v>
+        <v>0.2412314638022522</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7158,7 +7169,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.09738723264652971</v>
+        <v>-0.09597582347773947</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7166,22 +7177,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2214286163579581</v>
+        <v>0.2233286163579581</v>
       </c>
       <c r="C71">
-        <v>-3.115437665161966</v>
+        <v>-3.251301771040374</v>
       </c>
       <c r="D71">
-        <v>1.984032334838035</v>
+        <v>1.962798228959627</v>
       </c>
       <c r="E71">
-        <v>7.44647</v>
+        <v>7.561100000000001</v>
       </c>
       <c r="F71">
-        <v>7.90947</v>
+        <v>8.024100000000001</v>
       </c>
       <c r="G71">
         <v>2.81</v>
@@ -7202,37 +7213,37 @@
         <v>-0.179</v>
       </c>
       <c r="M71">
-        <v>1.865053026</v>
+        <v>1.89208278</v>
       </c>
       <c r="N71">
-        <v>-2.044053026</v>
+        <v>-2.07108278</v>
       </c>
       <c r="O71">
-        <v>-0.4905727262399999</v>
+        <v>-0.4970598672000001</v>
       </c>
       <c r="P71">
-        <v>-1.55348029976</v>
+        <v>-1.5740229128</v>
       </c>
       <c r="Q71">
-        <v>-1.10348029976</v>
+        <v>-1.1240229128</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1773513107561422</v>
+        <v>0.1817363544480136</v>
       </c>
       <c r="T71">
-        <v>1.81085330912716</v>
+        <v>1.871215086098066</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.02303419763465749</v>
+        <v>-0.0227051376684481</v>
       </c>
       <c r="W71">
-        <v>0.2412314638022522</v>
+        <v>0.2411538714622201</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7240,7 +7251,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.09597582347773947</v>
+        <v>-0.09460474028520038</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7248,22 +7259,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2233286163579581</v>
+        <v>0.2252286163579581</v>
       </c>
       <c r="C72">
-        <v>-3.251301771040374</v>
+        <v>-3.386716173833646</v>
       </c>
       <c r="D72">
-        <v>1.962798228959627</v>
+        <v>1.942013826166355</v>
       </c>
       <c r="E72">
-        <v>7.561100000000001</v>
+        <v>7.675730000000001</v>
       </c>
       <c r="F72">
-        <v>8.024100000000001</v>
+        <v>8.138730000000001</v>
       </c>
       <c r="G72">
         <v>2.81</v>
@@ -7284,37 +7295,37 @@
         <v>-0.179</v>
       </c>
       <c r="M72">
-        <v>1.89208278</v>
+        <v>1.919112534</v>
       </c>
       <c r="N72">
-        <v>-2.07108278</v>
+        <v>-2.098112534</v>
       </c>
       <c r="O72">
-        <v>-0.4970598672000001</v>
+        <v>-0.50354700816</v>
       </c>
       <c r="P72">
-        <v>-1.5740229128</v>
+        <v>-1.59456552584</v>
       </c>
       <c r="Q72">
-        <v>-1.1240229128</v>
+        <v>-1.14456552584</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1817363544480136</v>
+        <v>0.1864238149462209</v>
       </c>
       <c r="T72">
-        <v>1.871215086098066</v>
+        <v>1.935739744239378</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.0227051376684481</v>
+        <v>-0.0223853469970615</v>
       </c>
       <c r="W72">
-        <v>0.2411538714622201</v>
+        <v>0.2410784648219071</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7322,7 +7333,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.09460474028520038</v>
+        <v>-0.09327227915442293</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7330,22 +7341,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2252286163579581</v>
+        <v>0.2271286163579581</v>
       </c>
       <c r="C73">
-        <v>-3.386716173833644</v>
+        <v>-3.521695009796922</v>
       </c>
       <c r="D73">
-        <v>1.942013826166355</v>
+        <v>1.921664990203078</v>
       </c>
       <c r="E73">
-        <v>7.675729999999999</v>
+        <v>7.790359999999999</v>
       </c>
       <c r="F73">
-        <v>8.138729999999999</v>
+        <v>8.253359999999999</v>
       </c>
       <c r="G73">
         <v>2.81</v>
@@ -7366,37 +7377,37 @@
         <v>-0.179</v>
       </c>
       <c r="M73">
-        <v>1.919112534</v>
+        <v>1.946142288</v>
       </c>
       <c r="N73">
-        <v>-2.098112534</v>
+        <v>-2.125142288</v>
       </c>
       <c r="O73">
-        <v>-0.50354700816</v>
+        <v>-0.5100341491199999</v>
       </c>
       <c r="P73">
-        <v>-1.59456552584</v>
+        <v>-1.61510813888</v>
       </c>
       <c r="Q73">
-        <v>-1.14456552584</v>
+        <v>-1.16510813888</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1864238149462209</v>
+        <v>0.1914460940514431</v>
       </c>
       <c r="T73">
-        <v>1.935739744239378</v>
+        <v>2.004873306533641</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.02238534699706151</v>
+        <v>-0.0220744393998801</v>
       </c>
       <c r="W73">
-        <v>0.2410784648219071</v>
+        <v>0.2410051528104918</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7404,7 +7415,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.09327227915442293</v>
+        <v>-0.0919768308328337</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7412,22 +7423,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2271286163579581</v>
+        <v>0.2290286163579581</v>
       </c>
       <c r="C74">
-        <v>-3.521695009796922</v>
+        <v>-3.656251828838402</v>
       </c>
       <c r="D74">
-        <v>1.921664990203078</v>
+        <v>1.901738171161597</v>
       </c>
       <c r="E74">
-        <v>7.790359999999999</v>
+        <v>7.904989999999999</v>
       </c>
       <c r="F74">
-        <v>8.253359999999999</v>
+        <v>8.367989999999999</v>
       </c>
       <c r="G74">
         <v>2.81</v>
@@ -7448,37 +7459,37 @@
         <v>-0.179</v>
       </c>
       <c r="M74">
-        <v>1.946142288</v>
+        <v>1.973172042</v>
       </c>
       <c r="N74">
-        <v>-2.125142288</v>
+        <v>-2.152172042</v>
       </c>
       <c r="O74">
-        <v>-0.5100341491199999</v>
+        <v>-0.5165212900799999</v>
       </c>
       <c r="P74">
-        <v>-1.61510813888</v>
+        <v>-1.63565075192</v>
       </c>
       <c r="Q74">
-        <v>-1.16510813888</v>
+        <v>-1.18565075192</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1914460940514431</v>
+        <v>0.1968403938311261</v>
       </c>
       <c r="T74">
-        <v>2.004873306533641</v>
+        <v>2.079127873442295</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.0220744393998801</v>
+        <v>-0.02177204981905983</v>
       </c>
       <c r="W74">
-        <v>0.2410051528104918</v>
+        <v>0.2409338493473343</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7486,7 +7497,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.0919768308328337</v>
+        <v>-0.09071687424608244</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7494,22 +7505,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2290286163579581</v>
+        <v>0.2309286163579581</v>
       </c>
       <c r="C75">
-        <v>-3.656251828838402</v>
+        <v>-3.79039962460813</v>
       </c>
       <c r="D75">
-        <v>1.901738171161597</v>
+        <v>1.88222037539187</v>
       </c>
       <c r="E75">
-        <v>7.904989999999999</v>
+        <v>8.01962</v>
       </c>
       <c r="F75">
-        <v>8.367989999999999</v>
+        <v>8.482619999999999</v>
       </c>
       <c r="G75">
         <v>2.81</v>
@@ -7530,37 +7541,37 @@
         <v>-0.179</v>
       </c>
       <c r="M75">
-        <v>1.973172042</v>
+        <v>2.000201796</v>
       </c>
       <c r="N75">
-        <v>-2.152172042</v>
+        <v>-2.179201796</v>
       </c>
       <c r="O75">
-        <v>-0.5165212900799999</v>
+        <v>-0.5230084310399999</v>
       </c>
       <c r="P75">
-        <v>-1.63565075192</v>
+        <v>-1.65619336496</v>
       </c>
       <c r="Q75">
-        <v>-1.18565075192</v>
+        <v>-1.20619336496</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1968403938311261</v>
+        <v>0.2026496397477079</v>
       </c>
       <c r="T75">
-        <v>2.079127873442295</v>
+        <v>2.159094330113152</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.02177204981905983</v>
+        <v>-0.02147783292961307</v>
       </c>
       <c r="W75">
-        <v>0.2409338493473343</v>
+        <v>0.2408644730048028</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7568,7 +7579,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.09071687424608244</v>
+        <v>-0.08949097054005439</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7576,22 +7587,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2309286163579581</v>
+        <v>0.2328286163579581</v>
       </c>
       <c r="C76">
-        <v>-3.79039962460813</v>
+        <v>-3.924150862752778</v>
       </c>
       <c r="D76">
-        <v>1.88222037539187</v>
+        <v>1.863099137247221</v>
       </c>
       <c r="E76">
-        <v>8.01962</v>
+        <v>8.13425</v>
       </c>
       <c r="F76">
-        <v>8.482619999999999</v>
+        <v>8.597249999999999</v>
       </c>
       <c r="G76">
         <v>2.81</v>
@@ -7612,37 +7623,37 @@
         <v>-0.179</v>
       </c>
       <c r="M76">
-        <v>2.000201796</v>
+        <v>2.02723155</v>
       </c>
       <c r="N76">
-        <v>-2.179201796</v>
+        <v>-2.20623155</v>
       </c>
       <c r="O76">
-        <v>-0.5230084310399999</v>
+        <v>-0.5294955719999999</v>
       </c>
       <c r="P76">
-        <v>-1.65619336496</v>
+        <v>-1.676735978</v>
       </c>
       <c r="Q76">
-        <v>-1.20619336496</v>
+        <v>-1.226735978</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2026496397477079</v>
+        <v>0.2089236253376162</v>
       </c>
       <c r="T76">
-        <v>2.159094330113152</v>
+        <v>2.245458103317679</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.02147783292961307</v>
+        <v>-0.02119146182388489</v>
       </c>
       <c r="W76">
-        <v>0.2408644730048028</v>
+        <v>0.2407969466980721</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7650,7 +7661,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.08949097054005439</v>
+        <v>-0.0882977575995203</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7658,22 +7669,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2328286163579581</v>
+        <v>0.2347286163579581</v>
       </c>
       <c r="C77">
-        <v>-3.924150862752778</v>
+        <v>-4.057517507465525</v>
       </c>
       <c r="D77">
-        <v>1.863099137247221</v>
+        <v>1.844362492534475</v>
       </c>
       <c r="E77">
-        <v>8.13425</v>
+        <v>8.24888</v>
       </c>
       <c r="F77">
-        <v>8.597249999999999</v>
+        <v>8.711879999999999</v>
       </c>
       <c r="G77">
         <v>2.81</v>
@@ -7694,37 +7705,37 @@
         <v>-0.179</v>
       </c>
       <c r="M77">
-        <v>2.02723155</v>
+        <v>2.054261304</v>
       </c>
       <c r="N77">
-        <v>-2.20623155</v>
+        <v>-2.233261304</v>
       </c>
       <c r="O77">
-        <v>-0.5294955719999999</v>
+        <v>-0.5359827129599999</v>
       </c>
       <c r="P77">
-        <v>-1.676735978</v>
+        <v>-1.69727859104</v>
       </c>
       <c r="Q77">
-        <v>-1.226735978</v>
+        <v>-1.24727859104</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2089236253376162</v>
+        <v>0.2157204430600169</v>
       </c>
       <c r="T77">
-        <v>2.245458103317679</v>
+        <v>2.339018857622582</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.02119146182388489</v>
+        <v>-0.02091262679988641</v>
       </c>
       <c r="W77">
-        <v>0.2407969466980721</v>
+        <v>0.2407311973994132</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7732,7 +7743,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.0882977575995203</v>
+        <v>-0.08713594499952659</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7740,22 +7751,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2347286163579581</v>
+        <v>0.2366286163579581</v>
       </c>
       <c r="C78">
-        <v>-4.057517507465525</v>
+        <v>-4.190511046449856</v>
       </c>
       <c r="D78">
-        <v>1.844362492534475</v>
+        <v>1.825998953550143</v>
       </c>
       <c r="E78">
-        <v>8.24888</v>
+        <v>8.36351</v>
       </c>
       <c r="F78">
-        <v>8.711879999999999</v>
+        <v>8.826509999999999</v>
       </c>
       <c r="G78">
         <v>2.81</v>
@@ -7776,37 +7787,37 @@
         <v>-0.179</v>
       </c>
       <c r="M78">
-        <v>2.054261304</v>
+        <v>2.081291058</v>
       </c>
       <c r="N78">
-        <v>-2.233261304</v>
+        <v>-2.260291058</v>
       </c>
       <c r="O78">
-        <v>-0.5359827129599999</v>
+        <v>-0.5424698539199999</v>
       </c>
       <c r="P78">
-        <v>-1.69727859104</v>
+        <v>-1.71782120408</v>
       </c>
       <c r="Q78">
-        <v>-1.24727859104</v>
+        <v>-1.26782120408</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2157204430600169</v>
+        <v>0.2231082884104524</v>
       </c>
       <c r="T78">
-        <v>2.339018857622582</v>
+        <v>2.440715329693129</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.02091262679988641</v>
+        <v>-0.02064103424404373</v>
       </c>
       <c r="W78">
-        <v>0.2407311973994132</v>
+        <v>0.2406671558747455</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7814,7 +7825,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.08713594499952659</v>
+        <v>-0.08600430935018211</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7822,22 +7833,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2366286163579581</v>
+        <v>0.2385286163579581</v>
       </c>
       <c r="C79">
-        <v>-4.190511046449856</v>
+        <v>-4.323142514406756</v>
       </c>
       <c r="D79">
-        <v>1.825998953550143</v>
+        <v>1.807997485593243</v>
       </c>
       <c r="E79">
-        <v>8.36351</v>
+        <v>8.47814</v>
       </c>
       <c r="F79">
-        <v>8.826509999999999</v>
+        <v>8.941139999999999</v>
       </c>
       <c r="G79">
         <v>2.81</v>
@@ -7858,37 +7869,37 @@
         <v>-0.179</v>
       </c>
       <c r="M79">
-        <v>2.081291058</v>
+        <v>2.108320812</v>
       </c>
       <c r="N79">
-        <v>-2.260291058</v>
+        <v>-2.287320811999999</v>
       </c>
       <c r="O79">
-        <v>-0.5424698539199999</v>
+        <v>-0.5489569948799998</v>
       </c>
       <c r="P79">
-        <v>-1.71782120408</v>
+        <v>-1.73836381712</v>
       </c>
       <c r="Q79">
-        <v>-1.26782120408</v>
+        <v>-1.28836381712</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2231082884104524</v>
+        <v>0.231167756065473</v>
       </c>
       <c r="T79">
-        <v>2.440715329693129</v>
+        <v>2.551656935588271</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.02064103424404373</v>
+        <v>-0.02037640559988932</v>
       </c>
       <c r="W79">
-        <v>0.2406671558747455</v>
+        <v>0.2406047564404539</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7896,7 +7907,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.08600430935018211</v>
+        <v>-0.08490168999953873</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7904,22 +7915,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2385286163579581</v>
+        <v>0.2404286163579581</v>
       </c>
       <c r="C80">
-        <v>-4.323142514406756</v>
+        <v>-4.455422515146159</v>
       </c>
       <c r="D80">
-        <v>1.807997485593243</v>
+        <v>1.79034748485384</v>
       </c>
       <c r="E80">
-        <v>8.47814</v>
+        <v>8.59277</v>
       </c>
       <c r="F80">
-        <v>8.941139999999999</v>
+        <v>9.055769999999999</v>
       </c>
       <c r="G80">
         <v>2.81</v>
@@ -7940,37 +7951,37 @@
         <v>-0.179</v>
       </c>
       <c r="M80">
-        <v>2.108320812</v>
+        <v>2.135350566</v>
       </c>
       <c r="N80">
-        <v>-2.287320811999999</v>
+        <v>-2.314350566</v>
       </c>
       <c r="O80">
-        <v>-0.5489569948799998</v>
+        <v>-0.55544413584</v>
       </c>
       <c r="P80">
-        <v>-1.73836381712</v>
+        <v>-1.75890643016</v>
       </c>
       <c r="Q80">
-        <v>-1.28836381712</v>
+        <v>-1.30890643016</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.231167756065473</v>
+        <v>0.2399947920685908</v>
       </c>
       <c r="T80">
-        <v>2.551656935588271</v>
+        <v>2.673164408711522</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.02037640559988932</v>
+        <v>-0.02011847641508059</v>
       </c>
       <c r="W80">
-        <v>0.2406047564404539</v>
+        <v>0.240543936738676</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7978,7 +7989,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.08490168999953873</v>
+        <v>-0.0838269850628357</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7986,22 +7997,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2404286163579581</v>
+        <v>0.2423286163579581</v>
       </c>
       <c r="C81">
-        <v>-4.455422515146159</v>
+        <v>-4.587361242415812</v>
       </c>
       <c r="D81">
-        <v>1.79034748485384</v>
+        <v>1.773038757584186</v>
       </c>
       <c r="E81">
-        <v>8.59277</v>
+        <v>8.7074</v>
       </c>
       <c r="F81">
-        <v>9.055769999999999</v>
+        <v>9.170399999999999</v>
       </c>
       <c r="G81">
         <v>2.81</v>
@@ -8022,37 +8033,37 @@
         <v>-0.179</v>
       </c>
       <c r="M81">
-        <v>2.135350566</v>
+        <v>2.16238032</v>
       </c>
       <c r="N81">
-        <v>-2.314350566</v>
+        <v>-2.34138032</v>
       </c>
       <c r="O81">
-        <v>-0.55544413584</v>
+        <v>-0.5619312768</v>
       </c>
       <c r="P81">
-        <v>-1.75890643016</v>
+        <v>-1.7794490432</v>
       </c>
       <c r="Q81">
-        <v>-1.30890643016</v>
+        <v>-1.3294490432</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2399947920685908</v>
+        <v>0.2497045316720203</v>
       </c>
       <c r="T81">
-        <v>2.673164408711522</v>
+        <v>2.806822629147098</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.02011847641508059</v>
+        <v>-0.01986699545989209</v>
       </c>
       <c r="W81">
-        <v>0.240543936738676</v>
+        <v>0.2404846375294425</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8060,7 +8071,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.0838269850628357</v>
+        <v>-0.08277914774955031</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8068,22 +8079,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2423286163579581</v>
+        <v>0.2442286163579581</v>
       </c>
       <c r="C82">
-        <v>-4.587361242415812</v>
+        <v>-4.718968499533472</v>
       </c>
       <c r="D82">
-        <v>1.773038757584186</v>
+        <v>1.756061500466529</v>
       </c>
       <c r="E82">
-        <v>8.7074</v>
+        <v>8.822030000000002</v>
       </c>
       <c r="F82">
-        <v>9.170399999999999</v>
+        <v>9.285030000000001</v>
       </c>
       <c r="G82">
         <v>2.81</v>
@@ -8104,37 +8115,37 @@
         <v>-0.179</v>
       </c>
       <c r="M82">
-        <v>2.16238032</v>
+        <v>2.189410074</v>
       </c>
       <c r="N82">
-        <v>-2.34138032</v>
+        <v>-2.368410074</v>
       </c>
       <c r="O82">
-        <v>-0.5619312768</v>
+        <v>-0.56841841776</v>
       </c>
       <c r="P82">
-        <v>-1.7794490432</v>
+        <v>-1.79999165624</v>
       </c>
       <c r="Q82">
-        <v>-1.3294490432</v>
+        <v>-1.34999165624</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2497045316720203</v>
+        <v>0.2604363491284425</v>
       </c>
       <c r="T82">
-        <v>2.806822629147098</v>
+        <v>2.954550135944315</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.01986699545989209</v>
+        <v>-0.01962172391100453</v>
       </c>
       <c r="W82">
-        <v>0.2404846375294425</v>
+        <v>0.2404268024982149</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8142,7 +8153,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.08277914774955031</v>
+        <v>-0.08175718296251877</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8150,22 +8161,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2442286163579581</v>
+        <v>0.2461286163579581</v>
       </c>
       <c r="C83">
-        <v>-4.718968499533472</v>
+        <v>-4.850253717901897</v>
       </c>
       <c r="D83">
-        <v>1.756061500466529</v>
+        <v>1.739406282098103</v>
       </c>
       <c r="E83">
-        <v>8.822030000000002</v>
+        <v>8.936660000000002</v>
       </c>
       <c r="F83">
-        <v>9.285030000000001</v>
+        <v>9.399660000000001</v>
       </c>
       <c r="G83">
         <v>2.81</v>
@@ -8186,37 +8197,37 @@
         <v>-0.179</v>
       </c>
       <c r="M83">
-        <v>2.189410074</v>
+        <v>2.216439828</v>
       </c>
       <c r="N83">
-        <v>-2.368410074</v>
+        <v>-2.395439828</v>
       </c>
       <c r="O83">
-        <v>-0.56841841776</v>
+        <v>-0.57490555872</v>
       </c>
       <c r="P83">
-        <v>-1.79999165624</v>
+        <v>-1.82053426928</v>
       </c>
       <c r="Q83">
-        <v>-1.34999165624</v>
+        <v>-1.37053426928</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2604363491284425</v>
+        <v>0.2723605907466893</v>
       </c>
       <c r="T83">
-        <v>2.954550135944315</v>
+        <v>3.118691810163443</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.01962172391100453</v>
+        <v>-0.01938243459501667</v>
       </c>
       <c r="W83">
-        <v>0.2404268024982149</v>
+        <v>0.2403703780775049</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8224,7 +8235,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.08175718296251877</v>
+        <v>-0.08076014414590271</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8232,22 +8243,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2461286163579581</v>
+        <v>0.2480286163579581</v>
       </c>
       <c r="C84">
-        <v>-4.850253717901897</v>
+        <v>-4.981225974480148</v>
       </c>
       <c r="D84">
-        <v>1.739406282098103</v>
+        <v>1.723064025519852</v>
       </c>
       <c r="E84">
-        <v>8.936660000000002</v>
+        <v>9.051290000000002</v>
       </c>
       <c r="F84">
-        <v>9.399660000000001</v>
+        <v>9.514290000000001</v>
       </c>
       <c r="G84">
         <v>2.81</v>
@@ -8268,37 +8279,37 @@
         <v>-0.179</v>
       </c>
       <c r="M84">
-        <v>2.216439828</v>
+        <v>2.243469582</v>
       </c>
       <c r="N84">
-        <v>-2.395439828</v>
+        <v>-2.422469582</v>
       </c>
       <c r="O84">
-        <v>-0.57490555872</v>
+        <v>-0.5813926996800001</v>
       </c>
       <c r="P84">
-        <v>-1.82053426928</v>
+        <v>-1.84107688232</v>
       </c>
       <c r="Q84">
-        <v>-1.37053426928</v>
+        <v>-1.39107688232</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2723605907466893</v>
+        <v>0.2856876843200239</v>
       </c>
       <c r="T84">
-        <v>3.118691810163443</v>
+        <v>3.302144269584822</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.01938243459501667</v>
+        <v>-0.01914891128664297</v>
       </c>
       <c r="W84">
-        <v>0.2403703780775049</v>
+        <v>0.2403153132813904</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8306,7 +8317,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.08076014414590271</v>
+        <v>-0.07978713036101226</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8314,22 +8325,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2480286163579581</v>
+        <v>0.2499286163579581</v>
       </c>
       <c r="C85">
-        <v>-4.981225974480148</v>
+        <v>-5.111894008279127</v>
       </c>
       <c r="D85">
-        <v>1.723064025519852</v>
+        <v>1.707025991720873</v>
       </c>
       <c r="E85">
-        <v>9.051290000000002</v>
+        <v>9.165920000000002</v>
       </c>
       <c r="F85">
-        <v>9.514290000000001</v>
+        <v>9.628920000000001</v>
       </c>
       <c r="G85">
         <v>2.81</v>
@@ -8350,37 +8361,37 @@
         <v>-0.179</v>
       </c>
       <c r="M85">
-        <v>2.243469582</v>
+        <v>2.270499336</v>
       </c>
       <c r="N85">
-        <v>-2.422469582</v>
+        <v>-2.449499336</v>
       </c>
       <c r="O85">
-        <v>-0.5813926996800001</v>
+        <v>-0.58787984064</v>
       </c>
       <c r="P85">
-        <v>-1.84107688232</v>
+        <v>-1.86161949536</v>
       </c>
       <c r="Q85">
-        <v>-1.39107688232</v>
+        <v>-1.41161949536</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2856876843200239</v>
+        <v>0.3006806645900255</v>
       </c>
       <c r="T85">
-        <v>3.302144269584822</v>
+        <v>3.508528286433874</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.01914891128664297</v>
+        <v>-0.01892094805704008</v>
       </c>
       <c r="W85">
-        <v>0.2403153132813904</v>
+        <v>0.2402615595518501</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8388,7 +8399,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.07978713036101226</v>
+        <v>-0.07883728357100028</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8396,22 +8407,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2499286163579581</v>
+        <v>0.2518286163579581</v>
       </c>
       <c r="C86">
-        <v>-5.111894008279125</v>
+        <v>-5.242266235944406</v>
       </c>
       <c r="D86">
-        <v>1.707025991720873</v>
+        <v>1.691283764055593</v>
       </c>
       <c r="E86">
-        <v>9.16592</v>
+        <v>9.28055</v>
       </c>
       <c r="F86">
-        <v>9.628919999999999</v>
+        <v>9.743549999999999</v>
       </c>
       <c r="G86">
         <v>2.81</v>
@@ -8432,37 +8443,37 @@
         <v>-0.179</v>
       </c>
       <c r="M86">
-        <v>2.270499336</v>
+        <v>2.29752909</v>
       </c>
       <c r="N86">
-        <v>-2.449499336</v>
+        <v>-2.47652909</v>
       </c>
       <c r="O86">
-        <v>-0.5878798406399999</v>
+        <v>-0.5943669815999999</v>
       </c>
       <c r="P86">
-        <v>-1.86161949536</v>
+        <v>-1.8821621084</v>
       </c>
       <c r="Q86">
-        <v>-1.41161949536</v>
+        <v>-1.4321621084</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3006806645900253</v>
+        <v>0.3176727088960271</v>
       </c>
       <c r="T86">
-        <v>3.508528286433872</v>
+        <v>3.742430172196131</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.01892094805704008</v>
+        <v>-0.01869834866813373</v>
       </c>
       <c r="W86">
-        <v>0.2402615595518501</v>
+        <v>0.240209070615946</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8470,7 +8481,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.07883728357100028</v>
+        <v>-0.07790978611722377</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8478,22 +8489,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2518286163579581</v>
+        <v>0.2537286163579581</v>
       </c>
       <c r="C87">
-        <v>-5.242266235944406</v>
+        <v>-5.372350766484702</v>
       </c>
       <c r="D87">
-        <v>1.691283764055593</v>
+        <v>1.675829233515297</v>
       </c>
       <c r="E87">
-        <v>9.28055</v>
+        <v>9.39518</v>
       </c>
       <c r="F87">
-        <v>9.743549999999999</v>
+        <v>9.858179999999999</v>
       </c>
       <c r="G87">
         <v>2.81</v>
@@ -8514,37 +8525,37 @@
         <v>-0.179</v>
       </c>
       <c r="M87">
-        <v>2.29752909</v>
+        <v>2.324558844</v>
       </c>
       <c r="N87">
-        <v>-2.47652909</v>
+        <v>-2.503558844</v>
       </c>
       <c r="O87">
-        <v>-0.5943669815999999</v>
+        <v>-0.6008541225599999</v>
       </c>
       <c r="P87">
-        <v>-1.8821621084</v>
+        <v>-1.90270472144</v>
       </c>
       <c r="Q87">
-        <v>-1.4321621084</v>
+        <v>-1.45270472144</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3176727088960271</v>
+        <v>0.3370921881028862</v>
       </c>
       <c r="T87">
-        <v>3.742430172196131</v>
+        <v>4.009746613067283</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.01869834866813373</v>
+        <v>-0.01848092600920194</v>
       </c>
       <c r="W87">
-        <v>0.240209070615946</v>
+        <v>0.2401578023529699</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8552,7 +8563,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.07790978611722377</v>
+        <v>-0.07700385837167478</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8560,22 +8571,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2537286163579581</v>
+        <v>0.2556286163579581</v>
       </c>
       <c r="C88">
-        <v>-5.372350766484702</v>
+        <v>-5.502155415200143</v>
       </c>
       <c r="D88">
-        <v>1.675829233515297</v>
+        <v>1.660654584799856</v>
       </c>
       <c r="E88">
-        <v>9.39518</v>
+        <v>9.50981</v>
       </c>
       <c r="F88">
-        <v>9.858179999999999</v>
+        <v>9.972809999999999</v>
       </c>
       <c r="G88">
         <v>2.81</v>
@@ -8596,37 +8607,37 @@
         <v>-0.179</v>
       </c>
       <c r="M88">
-        <v>2.324558844</v>
+        <v>2.351588598</v>
       </c>
       <c r="N88">
-        <v>-2.503558844</v>
+        <v>-2.530588598</v>
       </c>
       <c r="O88">
-        <v>-0.6008541225599999</v>
+        <v>-0.6073412635199998</v>
       </c>
       <c r="P88">
-        <v>-1.90270472144</v>
+        <v>-1.92324733448</v>
       </c>
       <c r="Q88">
-        <v>-1.45270472144</v>
+        <v>-1.47324733448</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3370921881028862</v>
+        <v>0.3594992794954158</v>
       </c>
       <c r="T88">
-        <v>4.009746613067283</v>
+        <v>4.318188660226304</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.01848092600920194</v>
+        <v>-0.01826850157231456</v>
       </c>
       <c r="W88">
-        <v>0.2401578023529699</v>
+        <v>0.2401077126707518</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8634,7 +8645,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.07700385837167478</v>
+        <v>-0.07611875655131062</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8642,22 +8653,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2556286163579581</v>
+        <v>0.2575286163579581</v>
       </c>
       <c r="C89">
-        <v>-5.502155415200143</v>
+        <v>-5.63168771686061</v>
       </c>
       <c r="D89">
-        <v>1.660654584799856</v>
+        <v>1.645752283139388</v>
       </c>
       <c r="E89">
-        <v>9.50981</v>
+        <v>9.62444</v>
       </c>
       <c r="F89">
-        <v>9.972809999999999</v>
+        <v>10.08744</v>
       </c>
       <c r="G89">
         <v>2.81</v>
@@ -8678,37 +8689,37 @@
         <v>-0.179</v>
       </c>
       <c r="M89">
-        <v>2.351588598</v>
+        <v>2.378618352</v>
       </c>
       <c r="N89">
-        <v>-2.530588598</v>
+        <v>-2.557618352</v>
       </c>
       <c r="O89">
-        <v>-0.6073412635199998</v>
+        <v>-0.6138284044799999</v>
       </c>
       <c r="P89">
-        <v>-1.92324733448</v>
+        <v>-1.94378994752</v>
       </c>
       <c r="Q89">
-        <v>-1.47324733448</v>
+        <v>-1.49378994752</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3594992794954158</v>
+        <v>0.3856408861200339</v>
       </c>
       <c r="T89">
-        <v>4.318188660226304</v>
+        <v>4.678037715245164</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.01826850157231456</v>
+        <v>-0.01806090496353826</v>
       </c>
       <c r="W89">
-        <v>0.2401077126707518</v>
+        <v>0.2400587613904023</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8716,7 +8727,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.07611875655131062</v>
+        <v>-0.07525377068140937</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8724,22 +8735,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2575286163579581</v>
+        <v>0.2594286163579581</v>
       </c>
       <c r="C90">
-        <v>-5.63168771686061</v>
+        <v>-5.760954938180836</v>
       </c>
       <c r="D90">
-        <v>1.645752283139388</v>
+        <v>1.631115061819163</v>
       </c>
       <c r="E90">
-        <v>9.62444</v>
+        <v>9.73907</v>
       </c>
       <c r="F90">
-        <v>10.08744</v>
+        <v>10.20207</v>
       </c>
       <c r="G90">
         <v>2.81</v>
@@ -8760,37 +8771,37 @@
         <v>-0.179</v>
       </c>
       <c r="M90">
-        <v>2.378618352</v>
+        <v>2.405648106</v>
       </c>
       <c r="N90">
-        <v>-2.557618352</v>
+        <v>-2.584648106</v>
       </c>
       <c r="O90">
-        <v>-0.6138284044799999</v>
+        <v>-0.6203155454399999</v>
       </c>
       <c r="P90">
-        <v>-1.94378994752</v>
+        <v>-1.964332560559999</v>
       </c>
       <c r="Q90">
-        <v>-1.49378994752</v>
+        <v>-1.51433256056</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3856408861200339</v>
+        <v>0.416535512130946</v>
       </c>
       <c r="T90">
-        <v>4.678037715245164</v>
+        <v>5.103313871176542</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.01806090496353826</v>
+        <v>-0.01785797344709401</v>
       </c>
       <c r="W90">
-        <v>0.2400587613904023</v>
+        <v>0.2400109101388248</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8798,7 +8809,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.07525377068140937</v>
+        <v>-0.07440822269622505</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8806,22 +8817,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2594286163579581</v>
+        <v>0.2613286163579581</v>
       </c>
       <c r="C91">
-        <v>-5.760954938180836</v>
+        <v>-5.889964089635644</v>
       </c>
       <c r="D91">
-        <v>1.631115061819163</v>
+        <v>1.616735910364355</v>
       </c>
       <c r="E91">
-        <v>9.73907</v>
+        <v>9.8537</v>
       </c>
       <c r="F91">
-        <v>10.20207</v>
+        <v>10.3167</v>
       </c>
       <c r="G91">
         <v>2.81</v>
@@ -8842,37 +8853,37 @@
         <v>-0.179</v>
       </c>
       <c r="M91">
-        <v>2.405648106</v>
+        <v>2.43267786</v>
       </c>
       <c r="N91">
-        <v>-2.584648106</v>
+        <v>-2.61167786</v>
       </c>
       <c r="O91">
-        <v>-0.6203155454399999</v>
+        <v>-0.6268026863999999</v>
       </c>
       <c r="P91">
-        <v>-1.964332560559999</v>
+        <v>-1.9848751736</v>
       </c>
       <c r="Q91">
-        <v>-1.51433256056</v>
+        <v>-1.5348751736</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.416535512130946</v>
+        <v>0.4536090633440407</v>
       </c>
       <c r="T91">
-        <v>5.103313871176542</v>
+        <v>5.613645258294197</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.01785797344709401</v>
+        <v>-0.01765955151990408</v>
       </c>
       <c r="W91">
-        <v>0.2400109101388248</v>
+        <v>0.2399641222483934</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8880,7 +8891,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.07440822269622505</v>
+        <v>-0.07358146466626692</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8888,22 +8899,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2613286163579581</v>
+        <v>0.2632286163579581</v>
       </c>
       <c r="C92">
-        <v>-5.889964089635644</v>
+        <v>-6.018721936655721</v>
       </c>
       <c r="D92">
-        <v>1.616735910364355</v>
+        <v>1.602608063344277</v>
       </c>
       <c r="E92">
-        <v>9.8537</v>
+        <v>9.96833</v>
       </c>
       <c r="F92">
-        <v>10.3167</v>
+        <v>10.43133</v>
       </c>
       <c r="G92">
         <v>2.81</v>
@@ -8924,37 +8935,37 @@
         <v>-0.179</v>
       </c>
       <c r="M92">
-        <v>2.43267786</v>
+        <v>2.459707614</v>
       </c>
       <c r="N92">
-        <v>-2.61167786</v>
+        <v>-2.638707614</v>
       </c>
       <c r="O92">
-        <v>-0.6268026863999999</v>
+        <v>-0.6332898273599999</v>
       </c>
       <c r="P92">
-        <v>-1.9848751736</v>
+        <v>-2.00541778664</v>
       </c>
       <c r="Q92">
-        <v>-1.5348751736</v>
+        <v>-1.55541778664</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4536090633440407</v>
+        <v>0.4989211814933786</v>
       </c>
       <c r="T92">
-        <v>5.613645258294197</v>
+        <v>6.237383620326886</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.01765955151990408</v>
+        <v>-0.01746549051419085</v>
       </c>
       <c r="W92">
-        <v>0.2399641222483934</v>
+        <v>0.2399183626632462</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8962,7 +8973,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.07358146466626692</v>
+        <v>-0.07277287714246183</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8970,22 +8981,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2632286163579581</v>
+        <v>0.2651286163579581</v>
       </c>
       <c r="C93">
-        <v>-6.018721936655721</v>
+        <v>-6.147235010241452</v>
       </c>
       <c r="D93">
-        <v>1.602608063344277</v>
+        <v>1.588724989758547</v>
       </c>
       <c r="E93">
-        <v>9.96833</v>
+        <v>10.08296</v>
       </c>
       <c r="F93">
-        <v>10.43133</v>
+        <v>10.54596</v>
       </c>
       <c r="G93">
         <v>2.81</v>
@@ -9006,37 +9017,37 @@
         <v>-0.179</v>
       </c>
       <c r="M93">
-        <v>2.459707614</v>
+        <v>2.486737368</v>
       </c>
       <c r="N93">
-        <v>-2.638707614</v>
+        <v>-2.665737368</v>
       </c>
       <c r="O93">
-        <v>-0.6332898273599999</v>
+        <v>-0.63977696832</v>
       </c>
       <c r="P93">
-        <v>-2.00541778664</v>
+        <v>-2.02596039968</v>
       </c>
       <c r="Q93">
-        <v>-1.55541778664</v>
+        <v>-1.57596039968</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4989211814933786</v>
+        <v>0.5555613291800509</v>
       </c>
       <c r="T93">
-        <v>6.237383620326886</v>
+        <v>7.017056572867748</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.01746549051419085</v>
+        <v>-0.01727564822599312</v>
       </c>
       <c r="W93">
-        <v>0.2399183626632462</v>
+        <v>0.2398735978516892</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9044,7 +9055,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.07277287714246183</v>
+        <v>-0.07198186760830461</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9052,22 +9063,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2651286163579581</v>
+        <v>0.2670286163579582</v>
       </c>
       <c r="C94">
-        <v>-6.147235010241452</v>
+        <v>-6.275509617029831</v>
       </c>
       <c r="D94">
-        <v>1.588724989758547</v>
+        <v>1.575080382970168</v>
       </c>
       <c r="E94">
-        <v>10.08296</v>
+        <v>10.19759</v>
       </c>
       <c r="F94">
-        <v>10.54596</v>
+        <v>10.66059</v>
       </c>
       <c r="G94">
         <v>2.81</v>
@@ -9088,37 +9099,37 @@
         <v>-0.179</v>
       </c>
       <c r="M94">
-        <v>2.486737368</v>
+        <v>2.513767122</v>
       </c>
       <c r="N94">
-        <v>-2.665737368</v>
+        <v>-2.692767122</v>
       </c>
       <c r="O94">
-        <v>-0.63977696832</v>
+        <v>-0.6462641092799999</v>
       </c>
       <c r="P94">
-        <v>-2.02596039968</v>
+        <v>-2.04650301272</v>
       </c>
       <c r="Q94">
-        <v>-1.57596039968</v>
+        <v>-1.59650301272</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5555613291800509</v>
+        <v>0.6283843762057726</v>
       </c>
       <c r="T94">
-        <v>7.017056572867748</v>
+        <v>8.019493226134571</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.01727564822599312</v>
+        <v>-0.01708988856764911</v>
       </c>
       <c r="W94">
-        <v>0.2398735978516892</v>
+        <v>0.2398297957242517</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9126,7 +9137,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.07198186760830461</v>
+        <v>-0.07120786903187115</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9134,22 +9145,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2670286163579582</v>
+        <v>0.2689286163579581</v>
       </c>
       <c r="C95">
-        <v>-6.275509617029831</v>
+        <v>-6.403551848847027</v>
       </c>
       <c r="D95">
-        <v>1.575080382970168</v>
+        <v>1.561668151152972</v>
       </c>
       <c r="E95">
-        <v>10.19759</v>
+        <v>10.31222</v>
       </c>
       <c r="F95">
-        <v>10.66059</v>
+        <v>10.77522</v>
       </c>
       <c r="G95">
         <v>2.81</v>
@@ -9170,37 +9181,37 @@
         <v>-0.179</v>
       </c>
       <c r="M95">
-        <v>2.513767122</v>
+        <v>2.540796876</v>
       </c>
       <c r="N95">
-        <v>-2.692767122</v>
+        <v>-2.719796876</v>
       </c>
       <c r="O95">
-        <v>-0.6462641092799999</v>
+        <v>-0.6527512502399999</v>
       </c>
       <c r="P95">
-        <v>-2.04650301272</v>
+        <v>-2.06704562576</v>
       </c>
       <c r="Q95">
-        <v>-1.59650301272</v>
+        <v>-1.61704562576</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6283843762057726</v>
+        <v>0.7254817722400683</v>
       </c>
       <c r="T95">
-        <v>8.019493226134571</v>
+        <v>9.356075430490336</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.01708988856764911</v>
+        <v>-0.01690808124246135</v>
       </c>
       <c r="W95">
-        <v>0.2398297957242517</v>
+        <v>0.2397869255569724</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9208,7 +9219,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.07120786903187115</v>
+        <v>-0.07045033851025551</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9216,22 +9227,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2689286163579581</v>
+        <v>0.2708286163579581</v>
       </c>
       <c r="C96">
-        <v>-6.403551848847027</v>
+        <v>-6.531367591777032</v>
       </c>
       <c r="D96">
-        <v>1.561668151152972</v>
+        <v>1.548482408222967</v>
       </c>
       <c r="E96">
-        <v>10.31222</v>
+        <v>10.42685</v>
       </c>
       <c r="F96">
-        <v>10.77522</v>
+        <v>10.88985</v>
       </c>
       <c r="G96">
         <v>2.81</v>
@@ -9252,37 +9263,37 @@
         <v>-0.179</v>
       </c>
       <c r="M96">
-        <v>2.540796876</v>
+        <v>2.56782663</v>
       </c>
       <c r="N96">
-        <v>-2.719796876</v>
+        <v>-2.74682663</v>
       </c>
       <c r="O96">
-        <v>-0.6527512502399999</v>
+        <v>-0.6592383911999999</v>
       </c>
       <c r="P96">
-        <v>-2.06704562576</v>
+        <v>-2.0875882388</v>
       </c>
       <c r="Q96">
-        <v>-1.61704562576</v>
+        <v>-1.6375882388</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7254817722400683</v>
+        <v>0.8614181266880823</v>
       </c>
       <c r="T96">
-        <v>9.356075430490336</v>
+        <v>11.22729051658841</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.01690808124246135</v>
+        <v>-0.01673010143990912</v>
       </c>
       <c r="W96">
-        <v>0.2397869255569724</v>
+        <v>0.2397449579195306</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9290,7 +9301,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.07045033851025551</v>
+        <v>-0.06970875599962123</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9298,22 +9309,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2708286163579581</v>
+        <v>0.2727286163579581</v>
       </c>
       <c r="C97">
-        <v>-6.531367591777032</v>
+        <v>-6.658962534774714</v>
       </c>
       <c r="D97">
-        <v>1.548482408222967</v>
+        <v>1.535517465225286</v>
       </c>
       <c r="E97">
-        <v>10.42685</v>
+        <v>10.54148</v>
       </c>
       <c r="F97">
-        <v>10.88985</v>
+        <v>11.00448</v>
       </c>
       <c r="G97">
         <v>2.81</v>
@@ -9334,37 +9345,37 @@
         <v>-0.179</v>
       </c>
       <c r="M97">
-        <v>2.56782663</v>
+        <v>2.594856384</v>
       </c>
       <c r="N97">
-        <v>-2.74682663</v>
+        <v>-2.773856384</v>
       </c>
       <c r="O97">
-        <v>-0.6592383911999999</v>
+        <v>-0.66572553216</v>
       </c>
       <c r="P97">
-        <v>-2.0875882388</v>
+        <v>-2.10813085184</v>
       </c>
       <c r="Q97">
-        <v>-1.6375882388</v>
+        <v>-1.65813085184</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8614181266880823</v>
+        <v>1.065322658360103</v>
       </c>
       <c r="T97">
-        <v>11.22729051658841</v>
+        <v>14.03411314573551</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.01673010143990912</v>
+        <v>-0.01655582954991007</v>
       </c>
       <c r="W97">
-        <v>0.2397449579195306</v>
+        <v>0.2397038646078688</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9372,7 +9383,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.06970875599962123</v>
+        <v>-0.06898262312462533</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9380,22 +9391,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2727286163579581</v>
+        <v>0.2746286163579581</v>
       </c>
       <c r="C98">
-        <v>-6.658962534774712</v>
+        <v>-6.786342177849791</v>
       </c>
       <c r="D98">
-        <v>1.535517465225286</v>
+        <v>1.522767822150207</v>
       </c>
       <c r="E98">
-        <v>10.54148</v>
+        <v>10.65611</v>
       </c>
       <c r="F98">
-        <v>11.00448</v>
+        <v>11.11911</v>
       </c>
       <c r="G98">
         <v>2.81</v>
@@ -9416,37 +9427,37 @@
         <v>-0.179</v>
       </c>
       <c r="M98">
-        <v>2.594856384</v>
+        <v>2.621886138</v>
       </c>
       <c r="N98">
-        <v>-2.773856384</v>
+        <v>-2.800886138</v>
       </c>
       <c r="O98">
-        <v>-0.6657255321599999</v>
+        <v>-0.6722126731199999</v>
       </c>
       <c r="P98">
-        <v>-2.10813085184</v>
+        <v>-2.12867346488</v>
       </c>
       <c r="Q98">
-        <v>-1.65813085184</v>
+        <v>-1.67867346488</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.065322658360101</v>
+        <v>1.405163544480134</v>
       </c>
       <c r="T98">
-        <v>14.03411314573548</v>
+        <v>18.71215086098064</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.01655582954991007</v>
+        <v>-0.01638515089475636</v>
       </c>
       <c r="W98">
-        <v>0.2397038646078688</v>
+        <v>0.2396636185809836</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9454,7 +9465,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.06898262312462533</v>
+        <v>-0.06827146206148482</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9462,22 +9473,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2746286163579581</v>
+        <v>0.2765286163579581</v>
       </c>
       <c r="C99">
-        <v>-6.786342177849791</v>
+        <v>-6.91351183984645</v>
       </c>
       <c r="D99">
-        <v>1.522767822150207</v>
+        <v>1.510228160153549</v>
       </c>
       <c r="E99">
-        <v>10.65611</v>
+        <v>10.77074</v>
       </c>
       <c r="F99">
-        <v>11.11911</v>
+        <v>11.23374</v>
       </c>
       <c r="G99">
         <v>2.81</v>
@@ -9498,37 +9509,37 @@
         <v>-0.179</v>
       </c>
       <c r="M99">
-        <v>2.621886138</v>
+        <v>2.648915892</v>
       </c>
       <c r="N99">
-        <v>-2.800886138</v>
+        <v>-2.827915892</v>
       </c>
       <c r="O99">
-        <v>-0.6722126731199999</v>
+        <v>-0.6786998140799999</v>
       </c>
       <c r="P99">
-        <v>-2.12867346488</v>
+        <v>-2.14921607792</v>
       </c>
       <c r="Q99">
-        <v>-1.67867346488</v>
+        <v>-1.69921607792</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.405163544480134</v>
+        <v>2.084845316720201</v>
       </c>
       <c r="T99">
-        <v>18.71215086098064</v>
+        <v>28.06822629147095</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.01638515089475636</v>
+        <v>-0.01621795547746293</v>
       </c>
       <c r="W99">
-        <v>0.2396636185809836</v>
+        <v>0.2396241939015858</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9536,7 +9547,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.06827146206148482</v>
+        <v>-0.06757481448942881</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9544,22 +9555,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2765286163579581</v>
+        <v>0.2784286163579581</v>
       </c>
       <c r="C100">
-        <v>-6.91351183984645</v>
+        <v>-7.040476665841702</v>
       </c>
       <c r="D100">
-        <v>1.510228160153549</v>
+        <v>1.497893334158297</v>
       </c>
       <c r="E100">
-        <v>10.77074</v>
+        <v>10.88537</v>
       </c>
       <c r="F100">
-        <v>11.23374</v>
+        <v>11.34837</v>
       </c>
       <c r="G100">
         <v>2.81</v>
@@ -9580,37 +9591,37 @@
         <v>-0.179</v>
       </c>
       <c r="M100">
-        <v>2.648915892</v>
+        <v>2.675945646</v>
       </c>
       <c r="N100">
-        <v>-2.827915892</v>
+        <v>-2.854945646</v>
       </c>
       <c r="O100">
-        <v>-0.6786998140799999</v>
+        <v>-0.6851869550399998</v>
       </c>
       <c r="P100">
-        <v>-2.14921607792</v>
+        <v>-2.16975869096</v>
       </c>
       <c r="Q100">
-        <v>-1.69921607792</v>
+        <v>-1.71975869096</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.084845316720201</v>
+        <v>4.123890633440403</v>
       </c>
       <c r="T100">
-        <v>28.06822629147095</v>
+        <v>56.13645258294191</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.01621795547746293</v>
+        <v>-0.01605413774536735</v>
       </c>
       <c r="W100">
-        <v>0.2396241939015858</v>
+        <v>0.2395855656803576</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9618,91 +9629,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.06757481448942881</v>
+        <v>-0.06689224060569732</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2784286163579581</v>
-      </c>
-      <c r="C101">
-        <v>-7.040476665841702</v>
-      </c>
-      <c r="D101">
-        <v>1.497893334158297</v>
-      </c>
-      <c r="E101">
-        <v>10.88537</v>
-      </c>
-      <c r="F101">
-        <v>11.34837</v>
-      </c>
-      <c r="G101">
-        <v>2.81</v>
-      </c>
-      <c r="H101">
-        <v>11</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.271</v>
-      </c>
-      <c r="K101">
-        <v>0.45</v>
-      </c>
-      <c r="L101">
-        <v>-0.179</v>
-      </c>
-      <c r="M101">
-        <v>2.675945646</v>
-      </c>
-      <c r="N101">
-        <v>-2.854945646</v>
-      </c>
-      <c r="O101">
-        <v>-0.6851869550399998</v>
-      </c>
-      <c r="P101">
-        <v>-2.16975869096</v>
-      </c>
-      <c r="Q101">
-        <v>-1.71975869096</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.123890633440403</v>
-      </c>
-      <c r="T101">
-        <v>56.13645258294191</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.01605413774536735</v>
-      </c>
-      <c r="W101">
-        <v>0.2395855656803576</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.06689224060569732</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
